--- a/excel/2026/日前现货_发电侧小时电价.xlsx
+++ b/excel/2026/日前现货_发电侧小时电价.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z248"/>
+  <dimension ref="A1:Z260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,10 +565,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>46022</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -645,10 +647,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>46023</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -729,10 +729,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>46024</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -813,10 +811,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>46025</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -897,10 +893,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-01-04</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>46026</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -981,10 +975,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>46027</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1065,10 +1057,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
+      <c r="A8" s="2" t="n">
+        <v>46028</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1149,10 +1139,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
+      <c r="A9" s="2" t="n">
+        <v>46029</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1233,10 +1221,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
+      <c r="A10" s="2" t="n">
+        <v>46030</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1317,10 +1303,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-01-09</t>
-        </is>
+      <c r="A11" s="2" t="n">
+        <v>46031</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1401,10 +1385,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
+      <c r="A12" s="2" t="n">
+        <v>46032</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1485,10 +1467,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
+      <c r="A13" s="2" t="n">
+        <v>46033</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1569,10 +1549,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
+      <c r="A14" s="2" t="n">
+        <v>46034</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1653,10 +1631,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
+      <c r="A15" s="2" t="n">
+        <v>46035</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1737,10 +1713,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
+      <c r="A16" s="2" t="n">
+        <v>46036</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1821,10 +1795,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
+      <c r="A17" s="2" t="n">
+        <v>46037</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1905,10 +1877,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="A18" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1989,10 +1959,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-01-17</t>
-        </is>
+      <c r="A19" s="2" t="n">
+        <v>46039</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2073,10 +2041,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
+      <c r="A20" s="2" t="n">
+        <v>46040</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2157,10 +2123,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
+      <c r="A21" s="2" t="n">
+        <v>46041</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2241,10 +2205,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="A22" s="2" t="n">
+        <v>46042</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2325,10 +2287,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
+      <c r="A23" s="2" t="n">
+        <v>46043</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2409,10 +2369,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
+      <c r="A24" s="2" t="n">
+        <v>46044</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2493,10 +2451,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
+      <c r="A25" s="2" t="n">
+        <v>46045</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2577,10 +2533,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-01-24</t>
-        </is>
+      <c r="A26" s="2" t="n">
+        <v>46046</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2661,10 +2615,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
+      <c r="A27" s="2" t="n">
+        <v>46047</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2745,10 +2697,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
+      <c r="A28" s="2" t="n">
+        <v>46048</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2829,10 +2779,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
+      <c r="A29" s="2" t="n">
+        <v>46049</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2913,10 +2861,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
+      <c r="A30" s="2" t="n">
+        <v>46050</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2997,10 +2943,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
+      <c r="A31" s="2" t="n">
+        <v>46051</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3081,10 +3025,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="A32" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -3165,10 +3107,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
+      <c r="A33" s="2" t="n">
+        <v>46053</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3249,10 +3189,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
+      <c r="A34" s="2" t="n">
+        <v>46054</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3333,10 +3271,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
+      <c r="A35" s="2" t="n">
+        <v>46055</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3417,10 +3353,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
+      <c r="A36" s="2" t="n">
+        <v>46056</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3501,10 +3435,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="A37" s="2" t="n">
+        <v>46057</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3585,10 +3517,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
+      <c r="A38" s="2" t="n">
+        <v>46058</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3669,10 +3599,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="A39" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3753,10 +3681,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
+      <c r="A40" s="2" t="n">
+        <v>46060</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3837,10 +3763,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
+      <c r="A41" s="2" t="n">
+        <v>46061</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3921,10 +3845,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
+      <c r="A42" s="2" t="n">
+        <v>46062</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4005,10 +3927,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
+      <c r="A43" s="2" t="n">
+        <v>46063</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -4089,10 +4009,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
+      <c r="A44" s="2" t="n">
+        <v>46064</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4173,10 +4091,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
+      <c r="A45" s="2" t="n">
+        <v>46065</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -4257,10 +4173,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
+      <c r="A46" s="2" t="n">
+        <v>46066</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4341,10 +4255,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
+      <c r="A47" s="2" t="n">
+        <v>46067</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -4425,10 +4337,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
+      <c r="A48" s="2" t="n">
+        <v>46068</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4509,10 +4419,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
+      <c r="A49" s="2" t="n">
+        <v>46069</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -4593,10 +4501,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
+      <c r="A50" s="2" t="n">
+        <v>46070</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -4677,10 +4583,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
+      <c r="A51" s="2" t="n">
+        <v>46071</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -4761,10 +4665,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
+      <c r="A52" s="2" t="n">
+        <v>46072</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4845,10 +4747,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
+      <c r="A53" s="2" t="n">
+        <v>46073</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -4929,10 +4829,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
+      <c r="A54" s="2" t="n">
+        <v>46074</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -5013,10 +4911,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
+      <c r="A55" s="2" t="n">
+        <v>46075</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -5097,10 +4993,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
+      <c r="A56" s="2" t="n">
+        <v>46076</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -5181,10 +5075,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
+      <c r="A57" s="2" t="n">
+        <v>46077</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -5265,10 +5157,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
+      <c r="A58" s="2" t="n">
+        <v>46078</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -5349,10 +5239,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
+      <c r="A59" s="2" t="n">
+        <v>46079</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -5433,10 +5321,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
+      <c r="A60" s="2" t="n">
+        <v>46080</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -5517,10 +5403,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
+      <c r="A61" s="2" t="n">
+        <v>46081</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -5601,10 +5485,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="A62" s="2" t="n">
+        <v>46082</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -5685,10 +5567,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
+      <c r="A63" s="2" t="n">
+        <v>46083</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -5769,10 +5649,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
+      <c r="A64" s="2" t="n">
+        <v>46084</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -5853,10 +5731,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
+      <c r="A65" s="2" t="n">
+        <v>46085</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -5937,10 +5813,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
+      <c r="A66" s="2" t="n">
+        <v>46086</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -6021,10 +5895,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
+      <c r="A67" s="2" t="n">
+        <v>46087</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -6105,10 +5977,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
+      <c r="A68" s="2" t="n">
+        <v>46088</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -6189,10 +6059,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
+      <c r="A69" s="2" t="n">
+        <v>46089</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -6273,10 +6141,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
+      <c r="A70" s="2" t="n">
+        <v>46090</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -6357,10 +6223,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
+      <c r="A71" s="2" t="n">
+        <v>46091</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -6441,10 +6305,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
+      <c r="A72" s="2" t="n">
+        <v>46092</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -6525,10 +6387,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
+      <c r="A73" s="2" t="n">
+        <v>46093</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -6609,10 +6469,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
+      <c r="A74" s="2" t="n">
+        <v>46094</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -6693,10 +6551,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
+      <c r="A75" s="2" t="n">
+        <v>46095</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -6777,10 +6633,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
+      <c r="A76" s="2" t="n">
+        <v>46096</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -6861,10 +6715,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
+      <c r="A77" s="2" t="n">
+        <v>46097</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -6945,10 +6797,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
+      <c r="A78" s="2" t="n">
+        <v>46098</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -7029,10 +6879,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
+      <c r="A79" s="2" t="n">
+        <v>46099</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -7113,10 +6961,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
+      <c r="A80" s="2" t="n">
+        <v>46100</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -7197,10 +7043,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
+      <c r="A81" s="2" t="n">
+        <v>46101</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -7281,10 +7125,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
+      <c r="A82" s="2" t="n">
+        <v>46102</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -7365,10 +7207,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
+      <c r="A83" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -7449,10 +7289,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
+      <c r="A84" s="2" t="n">
+        <v>46104</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -7533,10 +7371,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
+      <c r="A85" s="2" t="n">
+        <v>46105</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -7617,10 +7453,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
+      <c r="A86" s="2" t="n">
+        <v>46106</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -7701,10 +7535,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
+      <c r="A87" s="2" t="n">
+        <v>46107</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -7785,10 +7617,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+      <c r="A88" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -7869,10 +7699,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
+      <c r="A89" s="2" t="n">
+        <v>46109</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -7953,10 +7781,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
+      <c r="A90" s="2" t="n">
+        <v>46110</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -8037,10 +7863,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
+      <c r="A91" s="2" t="n">
+        <v>46111</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -8121,10 +7945,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
+      <c r="A92" s="2" t="n">
+        <v>46112</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -8205,10 +8027,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
+      <c r="A93" s="2" t="n">
+        <v>46113</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -8289,10 +8109,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
+      <c r="A94" s="2" t="n">
+        <v>46114</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -8373,10 +8191,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
+      <c r="A95" s="2" t="n">
+        <v>46115</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -8457,10 +8273,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
+      <c r="A96" s="2" t="n">
+        <v>46116</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -8541,10 +8355,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
+      <c r="A97" s="2" t="n">
+        <v>46117</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -8625,10 +8437,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
+      <c r="A98" s="2" t="n">
+        <v>46118</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -8709,10 +8519,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
+      <c r="A99" s="2" t="n">
+        <v>46119</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -8793,10 +8601,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
+      <c r="A100" s="2" t="n">
+        <v>46120</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -8877,10 +8683,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
+      <c r="A101" s="2" t="n">
+        <v>46121</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -8961,10 +8765,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
+      <c r="A102" s="2" t="n">
+        <v>46122</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -9045,10 +8847,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
+      <c r="A103" s="2" t="n">
+        <v>46123</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -9129,10 +8929,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
+      <c r="A104" s="2" t="n">
+        <v>46124</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -9213,10 +9011,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
+      <c r="A105" s="2" t="n">
+        <v>46125</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -9297,10 +9093,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
+      <c r="A106" s="2" t="n">
+        <v>46126</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -9381,10 +9175,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
+      <c r="A107" s="2" t="n">
+        <v>46127</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -9465,10 +9257,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
+      <c r="A108" s="2" t="n">
+        <v>46128</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -9549,10 +9339,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
+      <c r="A109" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -9633,10 +9421,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
+      <c r="A110" s="2" t="n">
+        <v>46130</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -9717,10 +9503,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
+      <c r="A111" s="2" t="n">
+        <v>46131</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -9801,10 +9585,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
+      <c r="A112" s="2" t="n">
+        <v>46132</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -9885,10 +9667,8 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
+      <c r="A113" s="2" t="n">
+        <v>46133</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -9969,10 +9749,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
+      <c r="A114" s="2" t="n">
+        <v>46134</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -10053,10 +9831,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
+      <c r="A115" s="2" t="n">
+        <v>46135</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -10137,10 +9913,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
+      <c r="A116" s="2" t="n">
+        <v>46136</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -10221,10 +9995,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
+      <c r="A117" s="2" t="n">
+        <v>46137</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -10305,10 +10077,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
+      <c r="A118" s="2" t="n">
+        <v>46138</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -10389,10 +10159,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
+      <c r="A119" s="2" t="n">
+        <v>46139</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -10473,10 +10241,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
+      <c r="A120" s="2" t="n">
+        <v>46140</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -10557,10 +10323,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
+      <c r="A121" s="2" t="n">
+        <v>46141</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -10641,10 +10405,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
+      <c r="A122" s="2" t="n">
+        <v>46142</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -10725,10 +10487,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
+      <c r="A123" s="2" t="n">
+        <v>46143</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -10809,10 +10569,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
+      <c r="A124" s="2" t="n">
+        <v>46144</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -10893,10 +10651,8 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
+      <c r="A125" s="2" t="n">
+        <v>46145</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -10977,10 +10733,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
+      <c r="A126" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -11061,10 +10815,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
+      <c r="A127" s="2" t="n">
+        <v>46147</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -11145,10 +10897,8 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
+      <c r="A128" s="2" t="n">
+        <v>46148</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -11229,10 +10979,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
+      <c r="A129" s="2" t="n">
+        <v>46149</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -11313,10 +11061,8 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
+      <c r="A130" s="2" t="n">
+        <v>46150</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -11397,10 +11143,8 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
+      <c r="A131" s="2" t="n">
+        <v>46151</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -11481,10 +11225,8 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
+      <c r="A132" s="2" t="n">
+        <v>46152</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -11565,10 +11307,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
+      <c r="A133" s="2" t="n">
+        <v>46153</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -11649,10 +11389,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
+      <c r="A134" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -11733,10 +11471,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
+      <c r="A135" s="2" t="n">
+        <v>46155</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -11817,10 +11553,8 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
+      <c r="A136" s="2" t="n">
+        <v>46156</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -11901,10 +11635,8 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
+      <c r="A137" s="2" t="n">
+        <v>46157</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -11985,10 +11717,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
+      <c r="A138" s="2" t="n">
+        <v>46158</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -12069,10 +11799,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
+      <c r="A139" s="2" t="n">
+        <v>46159</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -12153,10 +11881,8 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+      <c r="A140" s="2" t="n">
+        <v>46160</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -12237,10 +11963,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
+      <c r="A141" s="2" t="n">
+        <v>46161</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -12321,10 +12045,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
+      <c r="A142" s="2" t="n">
+        <v>46162</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -12405,10 +12127,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
+      <c r="A143" s="2" t="n">
+        <v>46163</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -12489,10 +12209,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
+      <c r="A144" s="2" t="n">
+        <v>46164</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -12573,10 +12291,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
+      <c r="A145" s="2" t="n">
+        <v>46165</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -12657,10 +12373,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
+      <c r="A146" s="2" t="n">
+        <v>46166</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -12741,10 +12455,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
+      <c r="A147" s="2" t="n">
+        <v>46167</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -12825,10 +12537,8 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
+      <c r="A148" s="2" t="n">
+        <v>46168</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -12909,10 +12619,8 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
+      <c r="A149" s="2" t="n">
+        <v>46169</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -12993,10 +12701,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
+      <c r="A150" s="2" t="n">
+        <v>46170</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -13077,10 +12783,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
+      <c r="A151" s="2" t="n">
+        <v>46171</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -13161,10 +12865,8 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
+      <c r="A152" s="2" t="n">
+        <v>46172</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -13245,10 +12947,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
+      <c r="A153" s="2" t="n">
+        <v>46173</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -13329,10 +13029,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="A154" s="2" t="n">
+        <v>46174</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -13413,10 +13111,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
+      <c r="A155" s="2" t="n">
+        <v>46175</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -13497,10 +13193,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
+      <c r="A156" s="2" t="n">
+        <v>46176</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -13581,10 +13275,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
+      <c r="A157" s="2" t="n">
+        <v>46177</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -13665,10 +13357,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
+      <c r="A158" s="2" t="n">
+        <v>46178</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -13749,10 +13439,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
+      <c r="A159" s="2" t="n">
+        <v>46179</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -13833,10 +13521,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
+      <c r="A160" s="2" t="n">
+        <v>46180</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -13917,10 +13603,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
+      <c r="A161" s="2" t="n">
+        <v>46181</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -14001,10 +13685,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
+      <c r="A162" s="2" t="n">
+        <v>46182</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -14085,10 +13767,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
+      <c r="A163" s="2" t="n">
+        <v>46183</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -14169,10 +13849,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
+      <c r="A164" s="2" t="n">
+        <v>46184</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -14253,10 +13931,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
+      <c r="A165" s="2" t="n">
+        <v>46185</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -14337,10 +14013,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
+      <c r="A166" s="2" t="n">
+        <v>46186</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -14421,10 +14095,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
+      <c r="A167" s="2" t="n">
+        <v>46187</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -14505,10 +14177,8 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
+      <c r="A168" s="2" t="n">
+        <v>46188</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -14589,10 +14259,8 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
+      <c r="A169" s="2" t="n">
+        <v>46189</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -14673,10 +14341,8 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
+      <c r="A170" s="2" t="n">
+        <v>46190</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -14757,10 +14423,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
+      <c r="A171" s="2" t="n">
+        <v>46191</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -14841,10 +14505,8 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+      <c r="A172" s="2" t="n">
+        <v>46192</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -14925,10 +14587,8 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
+      <c r="A173" s="2" t="n">
+        <v>46193</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -15009,10 +14669,8 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
+      <c r="A174" s="2" t="n">
+        <v>46194</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -15093,10 +14751,8 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
+      <c r="A175" s="2" t="n">
+        <v>46195</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -15177,10 +14833,8 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
+      <c r="A176" s="2" t="n">
+        <v>46196</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -15261,10 +14915,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
+      <c r="A177" s="2" t="n">
+        <v>46197</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -15345,10 +14997,8 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
+      <c r="A178" s="2" t="n">
+        <v>46198</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -15429,10 +15079,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
+      <c r="A179" s="2" t="n">
+        <v>46199</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -15513,10 +15161,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
+      <c r="A180" s="2" t="n">
+        <v>46200</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -15597,10 +15243,8 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
+      <c r="A181" s="2" t="n">
+        <v>46201</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -15681,10 +15325,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
+      <c r="A182" s="2" t="n">
+        <v>46202</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -15765,10 +15407,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
+      <c r="A183" s="2" t="n">
+        <v>46203</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -15849,10 +15489,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
+      <c r="A184" s="2" t="n">
+        <v>46204</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -15933,10 +15571,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
+      <c r="A185" s="2" t="n">
+        <v>46205</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -16017,10 +15653,8 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
+      <c r="A186" s="2" t="n">
+        <v>46206</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -16101,10 +15735,8 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
+      <c r="A187" s="2" t="n">
+        <v>46207</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -16185,10 +15817,8 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
+      <c r="A188" s="2" t="n">
+        <v>46208</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -16269,10 +15899,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
+      <c r="A189" s="2" t="n">
+        <v>46209</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -16353,10 +15981,8 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
+      <c r="A190" s="2" t="n">
+        <v>46210</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -16437,10 +16063,8 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
+      <c r="A191" s="2" t="n">
+        <v>46211</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -16521,10 +16145,8 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
+      <c r="A192" s="2" t="n">
+        <v>46212</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -16605,10 +16227,8 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
+      <c r="A193" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -16689,10 +16309,8 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
+      <c r="A194" s="2" t="n">
+        <v>46214</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -16773,10 +16391,8 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
+      <c r="A195" s="2" t="n">
+        <v>46215</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -16857,10 +16473,8 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
+      <c r="A196" s="2" t="n">
+        <v>46216</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -16941,10 +16555,8 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
+      <c r="A197" s="2" t="n">
+        <v>46217</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -17025,10 +16637,8 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
+      <c r="A198" s="2" t="n">
+        <v>46218</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -17109,10 +16719,8 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
+      <c r="A199" s="2" t="n">
+        <v>46219</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -17193,10 +16801,8 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
+      <c r="A200" s="2" t="n">
+        <v>46220</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -17277,10 +16883,8 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
+      <c r="A201" s="2" t="n">
+        <v>46221</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -17361,10 +16965,8 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
+      <c r="A202" s="2" t="n">
+        <v>46222</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -17445,10 +17047,8 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
+      <c r="A203" s="2" t="n">
+        <v>46223</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -17529,10 +17129,8 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
+      <c r="A204" s="2" t="n">
+        <v>46224</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -17613,10 +17211,8 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
+      <c r="A205" s="2" t="n">
+        <v>46225</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -17697,10 +17293,8 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
+      <c r="A206" s="2" t="n">
+        <v>46226</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -17781,10 +17375,8 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
+      <c r="A207" s="2" t="n">
+        <v>46227</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -17865,10 +17457,8 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
+      <c r="A208" s="2" t="n">
+        <v>46228</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -17949,10 +17539,8 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
+      <c r="A209" s="2" t="n">
+        <v>46229</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -18033,10 +17621,8 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
+      <c r="A210" s="2" t="n">
+        <v>46230</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -18117,10 +17703,8 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+      <c r="A211" s="2" t="n">
+        <v>46231</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -18201,10 +17785,8 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+      <c r="A212" s="2" t="n">
+        <v>46232</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -18285,10 +17867,8 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
+      <c r="A213" s="2" t="n">
+        <v>46233</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -18369,10 +17949,8 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
+      <c r="A214" s="2" t="n">
+        <v>46234</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -18453,10 +18031,8 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
+      <c r="A215" s="2" t="n">
+        <v>46235</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -18537,10 +18113,8 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+      <c r="A216" s="2" t="n">
+        <v>46236</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -18621,10 +18195,8 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
+      <c r="A217" s="2" t="n">
+        <v>46237</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -18705,10 +18277,8 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
+      <c r="A218" s="2" t="n">
+        <v>46238</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -18789,10 +18359,8 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
+      <c r="A219" s="2" t="n">
+        <v>46239</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -18873,10 +18441,8 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
+      <c r="A220" s="2" t="n">
+        <v>46240</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -18957,10 +18523,8 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+      <c r="A221" s="2" t="n">
+        <v>46241</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -19041,10 +18605,8 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
+      <c r="A222" s="2" t="n">
+        <v>46242</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -19125,10 +18687,8 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
+      <c r="A223" s="2" t="n">
+        <v>46243</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -19209,10 +18769,8 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
+      <c r="A224" s="2" t="n">
+        <v>46244</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -19293,10 +18851,8 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
+      <c r="A225" s="2" t="n">
+        <v>46245</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -19377,10 +18933,8 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+      <c r="A226" s="2" t="n">
+        <v>46246</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -19461,10 +19015,8 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
+      <c r="A227" s="2" t="n">
+        <v>46247</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -19545,10 +19097,8 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+      <c r="A228" s="2" t="n">
+        <v>46248</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -19629,10 +19179,8 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
+      <c r="A229" s="2" t="n">
+        <v>46249</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -19713,10 +19261,8 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
+      <c r="A230" s="2" t="n">
+        <v>46250</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -19797,10 +19343,8 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
+      <c r="A231" s="2" t="n">
+        <v>46251</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -19881,10 +19425,8 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
+      <c r="A232" s="2" t="n">
+        <v>46252</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -19965,10 +19507,8 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
+      <c r="A233" s="2" t="n">
+        <v>46253</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -20049,10 +19589,8 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
+      <c r="A234" s="2" t="n">
+        <v>46254</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -20133,10 +19671,8 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
+      <c r="A235" s="2" t="n">
+        <v>46255</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -20217,10 +19753,8 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
+      <c r="A236" s="2" t="n">
+        <v>46256</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -20301,10 +19835,8 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
+      <c r="A237" s="2" t="n">
+        <v>46257</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -20385,10 +19917,8 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
+      <c r="A238" s="2" t="n">
+        <v>46258</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -20469,10 +19999,8 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
+      <c r="A239" s="2" t="n">
+        <v>46259</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -20553,10 +20081,8 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
+      <c r="A240" s="2" t="n">
+        <v>46260</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -20637,10 +20163,8 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
+      <c r="A241" s="2" t="n">
+        <v>46261</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -20721,10 +20245,8 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
+      <c r="A242" s="2" t="n">
+        <v>46262</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -20805,10 +20327,8 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
+      <c r="A243" s="2" t="n">
+        <v>46263</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -20889,10 +20409,8 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
+      <c r="A244" s="2" t="n">
+        <v>46264</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -20973,10 +20491,8 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
+      <c r="A245" s="2" t="n">
+        <v>46265</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -21057,10 +20573,8 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
+      <c r="A246" s="2" t="n">
+        <v>46266</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -21141,10 +20655,8 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
+      <c r="A247" s="2" t="n">
+        <v>46267</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -21225,10 +20737,8 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
+      <c r="A248" s="2" t="n">
+        <v>46268</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -21306,6 +20816,942 @@
       </c>
       <c r="Z248" t="n">
         <v>550</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="n">
+        <v>539.95</v>
+      </c>
+      <c r="D249" t="n">
+        <v>529.95</v>
+      </c>
+      <c r="E249" t="n">
+        <v>514.49</v>
+      </c>
+      <c r="F249" t="n">
+        <v>504.45</v>
+      </c>
+      <c r="G249" t="n">
+        <v>504.45</v>
+      </c>
+      <c r="H249" t="n">
+        <v>512.5</v>
+      </c>
+      <c r="I249" t="n">
+        <v>433.14</v>
+      </c>
+      <c r="J249" t="n">
+        <v>256</v>
+      </c>
+      <c r="K249" t="n">
+        <v>50</v>
+      </c>
+      <c r="L249" t="n">
+        <v>55</v>
+      </c>
+      <c r="M249" t="n">
+        <v>100</v>
+      </c>
+      <c r="N249" t="n">
+        <v>100</v>
+      </c>
+      <c r="O249" t="n">
+        <v>100</v>
+      </c>
+      <c r="P249" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>124.03</v>
+      </c>
+      <c r="R249" t="n">
+        <v>242.65</v>
+      </c>
+      <c r="S249" t="n">
+        <v>439.5</v>
+      </c>
+      <c r="T249" t="n">
+        <v>524.4400000000001</v>
+      </c>
+      <c r="U249" t="n">
+        <v>527.34</v>
+      </c>
+      <c r="V249" t="n">
+        <v>515</v>
+      </c>
+      <c r="W249" t="n">
+        <v>516.14</v>
+      </c>
+      <c r="X249" t="n">
+        <v>517.26</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>516.1799999999999</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>522.17</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="n">
+        <v>530</v>
+      </c>
+      <c r="D250" t="n">
+        <v>529.5</v>
+      </c>
+      <c r="E250" t="n">
+        <v>495</v>
+      </c>
+      <c r="F250" t="n">
+        <v>492.38</v>
+      </c>
+      <c r="G250" t="n">
+        <v>500</v>
+      </c>
+      <c r="H250" t="n">
+        <v>504</v>
+      </c>
+      <c r="I250" t="n">
+        <v>400</v>
+      </c>
+      <c r="J250" t="n">
+        <v>273.56</v>
+      </c>
+      <c r="K250" t="n">
+        <v>141.12</v>
+      </c>
+      <c r="L250" t="n">
+        <v>154.59</v>
+      </c>
+      <c r="M250" t="n">
+        <v>250</v>
+      </c>
+      <c r="N250" t="n">
+        <v>300</v>
+      </c>
+      <c r="O250" t="n">
+        <v>300</v>
+      </c>
+      <c r="P250" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>280</v>
+      </c>
+      <c r="R250" t="n">
+        <v>352</v>
+      </c>
+      <c r="S250" t="n">
+        <v>489.5</v>
+      </c>
+      <c r="T250" t="n">
+        <v>553.5</v>
+      </c>
+      <c r="U250" t="n">
+        <v>525</v>
+      </c>
+      <c r="V250" t="n">
+        <v>529.95</v>
+      </c>
+      <c r="W250" t="n">
+        <v>525</v>
+      </c>
+      <c r="X250" t="n">
+        <v>544.5</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>547.2</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="n">
+        <v>510.9</v>
+      </c>
+      <c r="D251" t="n">
+        <v>500</v>
+      </c>
+      <c r="E251" t="n">
+        <v>478.09</v>
+      </c>
+      <c r="F251" t="n">
+        <v>476.35</v>
+      </c>
+      <c r="G251" t="n">
+        <v>484.9</v>
+      </c>
+      <c r="H251" t="n">
+        <v>484.95</v>
+      </c>
+      <c r="I251" t="n">
+        <v>420.82</v>
+      </c>
+      <c r="J251" t="n">
+        <v>352.1</v>
+      </c>
+      <c r="K251" t="n">
+        <v>300</v>
+      </c>
+      <c r="L251" t="n">
+        <v>272.5</v>
+      </c>
+      <c r="M251" t="n">
+        <v>282.59</v>
+      </c>
+      <c r="N251" t="n">
+        <v>291</v>
+      </c>
+      <c r="O251" t="n">
+        <v>290</v>
+      </c>
+      <c r="P251" t="n">
+        <v>291</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>331.08</v>
+      </c>
+      <c r="R251" t="n">
+        <v>390.02</v>
+      </c>
+      <c r="S251" t="n">
+        <v>462.95</v>
+      </c>
+      <c r="T251" t="n">
+        <v>509.85</v>
+      </c>
+      <c r="U251" t="n">
+        <v>500</v>
+      </c>
+      <c r="V251" t="n">
+        <v>499.8</v>
+      </c>
+      <c r="W251" t="n">
+        <v>484.95</v>
+      </c>
+      <c r="X251" t="n">
+        <v>484.95</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>478.65</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>463.15</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="n">
+        <v>413.65</v>
+      </c>
+      <c r="D252" t="n">
+        <v>400</v>
+      </c>
+      <c r="E252" t="n">
+        <v>390.17</v>
+      </c>
+      <c r="F252" t="n">
+        <v>357</v>
+      </c>
+      <c r="G252" t="n">
+        <v>362</v>
+      </c>
+      <c r="H252" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="I252" t="n">
+        <v>349.5</v>
+      </c>
+      <c r="J252" t="n">
+        <v>320</v>
+      </c>
+      <c r="K252" t="n">
+        <v>310</v>
+      </c>
+      <c r="L252" t="n">
+        <v>303.5</v>
+      </c>
+      <c r="M252" t="n">
+        <v>319</v>
+      </c>
+      <c r="N252" t="n">
+        <v>325</v>
+      </c>
+      <c r="O252" t="n">
+        <v>300</v>
+      </c>
+      <c r="P252" t="n">
+        <v>314.15</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>350</v>
+      </c>
+      <c r="R252" t="n">
+        <v>360</v>
+      </c>
+      <c r="S252" t="n">
+        <v>337</v>
+      </c>
+      <c r="T252" t="n">
+        <v>400</v>
+      </c>
+      <c r="U252" t="n">
+        <v>401.31</v>
+      </c>
+      <c r="V252" t="n">
+        <v>400</v>
+      </c>
+      <c r="W252" t="n">
+        <v>370.91</v>
+      </c>
+      <c r="X252" t="n">
+        <v>381.5</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>390.36</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="D253" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="E253" t="n">
+        <v>380</v>
+      </c>
+      <c r="F253" t="n">
+        <v>372.79</v>
+      </c>
+      <c r="G253" t="n">
+        <v>375</v>
+      </c>
+      <c r="H253" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="I253" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="J253" t="n">
+        <v>350</v>
+      </c>
+      <c r="K253" t="n">
+        <v>361</v>
+      </c>
+      <c r="L253" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="M253" t="n">
+        <v>379.5</v>
+      </c>
+      <c r="N253" t="n">
+        <v>375</v>
+      </c>
+      <c r="O253" t="n">
+        <v>350</v>
+      </c>
+      <c r="P253" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>370</v>
+      </c>
+      <c r="R253" t="n">
+        <v>390.5</v>
+      </c>
+      <c r="S253" t="n">
+        <v>399</v>
+      </c>
+      <c r="T253" t="n">
+        <v>451.48</v>
+      </c>
+      <c r="U253" t="n">
+        <v>455</v>
+      </c>
+      <c r="V253" t="n">
+        <v>454.84</v>
+      </c>
+      <c r="W253" t="n">
+        <v>455.5</v>
+      </c>
+      <c r="X253" t="n">
+        <v>472.95</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>467.57</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>480.48</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="n">
+        <v>471.32</v>
+      </c>
+      <c r="D254" t="n">
+        <v>462.42</v>
+      </c>
+      <c r="E254" t="n">
+        <v>445.33</v>
+      </c>
+      <c r="F254" t="n">
+        <v>440</v>
+      </c>
+      <c r="G254" t="n">
+        <v>440</v>
+      </c>
+      <c r="H254" t="n">
+        <v>459.5</v>
+      </c>
+      <c r="I254" t="n">
+        <v>423.5</v>
+      </c>
+      <c r="J254" t="n">
+        <v>330</v>
+      </c>
+      <c r="K254" t="n">
+        <v>279.5</v>
+      </c>
+      <c r="L254" t="n">
+        <v>151.6</v>
+      </c>
+      <c r="M254" t="n">
+        <v>200</v>
+      </c>
+      <c r="N254" t="n">
+        <v>200</v>
+      </c>
+      <c r="O254" t="n">
+        <v>187.09</v>
+      </c>
+      <c r="P254" t="n">
+        <v>152.17</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>200</v>
+      </c>
+      <c r="R254" t="n">
+        <v>315</v>
+      </c>
+      <c r="S254" t="n">
+        <v>450</v>
+      </c>
+      <c r="T254" t="n">
+        <v>500</v>
+      </c>
+      <c r="U254" t="n">
+        <v>502.53</v>
+      </c>
+      <c r="V254" t="n">
+        <v>502.5</v>
+      </c>
+      <c r="W254" t="n">
+        <v>500</v>
+      </c>
+      <c r="X254" t="n">
+        <v>504.6</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" t="n">
+        <v>483.13</v>
+      </c>
+      <c r="D255" t="n">
+        <v>471</v>
+      </c>
+      <c r="E255" t="n">
+        <v>460</v>
+      </c>
+      <c r="F255" t="n">
+        <v>460</v>
+      </c>
+      <c r="G255" t="n">
+        <v>459.15</v>
+      </c>
+      <c r="H255" t="n">
+        <v>464.1</v>
+      </c>
+      <c r="I255" t="n">
+        <v>439.49</v>
+      </c>
+      <c r="J255" t="n">
+        <v>372.23</v>
+      </c>
+      <c r="K255" t="n">
+        <v>319</v>
+      </c>
+      <c r="L255" t="n">
+        <v>279.5</v>
+      </c>
+      <c r="M255" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="N255" t="n">
+        <v>238.35</v>
+      </c>
+      <c r="O255" t="n">
+        <v>200.98</v>
+      </c>
+      <c r="P255" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>302.5</v>
+      </c>
+      <c r="R255" t="n">
+        <v>357</v>
+      </c>
+      <c r="S255" t="n">
+        <v>421.48</v>
+      </c>
+      <c r="T255" t="n">
+        <v>483.03</v>
+      </c>
+      <c r="U255" t="n">
+        <v>488.27</v>
+      </c>
+      <c r="V255" t="n">
+        <v>479</v>
+      </c>
+      <c r="W255" t="n">
+        <v>477.2</v>
+      </c>
+      <c r="X255" t="n">
+        <v>478</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>471.98</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>464.7</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" t="n">
+        <v>450</v>
+      </c>
+      <c r="D256" t="n">
+        <v>430.36</v>
+      </c>
+      <c r="E256" t="n">
+        <v>434.18</v>
+      </c>
+      <c r="F256" t="n">
+        <v>427.94</v>
+      </c>
+      <c r="G256" t="n">
+        <v>433.24</v>
+      </c>
+      <c r="H256" t="n">
+        <v>439.9</v>
+      </c>
+      <c r="I256" t="n">
+        <v>395</v>
+      </c>
+      <c r="J256" t="n">
+        <v>379.51</v>
+      </c>
+      <c r="K256" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="L256" t="n">
+        <v>321.75</v>
+      </c>
+      <c r="M256" t="n">
+        <v>327.39</v>
+      </c>
+      <c r="N256" t="n">
+        <v>329.1</v>
+      </c>
+      <c r="O256" t="n">
+        <v>300</v>
+      </c>
+      <c r="P256" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>335.13</v>
+      </c>
+      <c r="R256" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="S256" t="n">
+        <v>445</v>
+      </c>
+      <c r="T256" t="n">
+        <v>469.5</v>
+      </c>
+      <c r="U256" t="n">
+        <v>474</v>
+      </c>
+      <c r="V256" t="n">
+        <v>450.57</v>
+      </c>
+      <c r="W256" t="n">
+        <v>449.5</v>
+      </c>
+      <c r="X256" t="n">
+        <v>449.5</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>440</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>443.6</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="n">
+        <v>430</v>
+      </c>
+      <c r="D257" t="n">
+        <v>430</v>
+      </c>
+      <c r="E257" t="n">
+        <v>416.73</v>
+      </c>
+      <c r="F257" t="n">
+        <v>415</v>
+      </c>
+      <c r="G257" t="n">
+        <v>419.5</v>
+      </c>
+      <c r="H257" t="n">
+        <v>424</v>
+      </c>
+      <c r="I257" t="n">
+        <v>394.78</v>
+      </c>
+      <c r="J257" t="n">
+        <v>383.29</v>
+      </c>
+      <c r="K257" t="n">
+        <v>369.5</v>
+      </c>
+      <c r="L257" t="n">
+        <v>340</v>
+      </c>
+      <c r="M257" t="n">
+        <v>355</v>
+      </c>
+      <c r="N257" t="n">
+        <v>331.5</v>
+      </c>
+      <c r="O257" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="P257" t="n">
+        <v>310</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>350</v>
+      </c>
+      <c r="R257" t="n">
+        <v>404</v>
+      </c>
+      <c r="S257" t="n">
+        <v>440.86</v>
+      </c>
+      <c r="T257" t="n">
+        <v>475</v>
+      </c>
+      <c r="U257" t="n">
+        <v>475.05</v>
+      </c>
+      <c r="V257" t="n">
+        <v>451.85</v>
+      </c>
+      <c r="W257" t="n">
+        <v>459</v>
+      </c>
+      <c r="X257" t="n">
+        <v>450</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>450</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="n">
+        <v>484.5</v>
+      </c>
+      <c r="D258" t="n">
+        <v>482.12</v>
+      </c>
+      <c r="E258" t="n">
+        <v>474</v>
+      </c>
+      <c r="F258" t="n">
+        <v>457.04</v>
+      </c>
+      <c r="G258" t="n">
+        <v>458.41</v>
+      </c>
+      <c r="H258" t="n">
+        <v>464.97</v>
+      </c>
+      <c r="I258" t="n">
+        <v>398.85</v>
+      </c>
+      <c r="J258" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="K258" t="n">
+        <v>113.41</v>
+      </c>
+      <c r="L258" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="M258" t="n">
+        <v>59</v>
+      </c>
+      <c r="N258" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="O258" t="n">
+        <v>108.26</v>
+      </c>
+      <c r="P258" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>66.54000000000001</v>
+      </c>
+      <c r="R258" t="n">
+        <v>250</v>
+      </c>
+      <c r="S258" t="n">
+        <v>436</v>
+      </c>
+      <c r="T258" t="n">
+        <v>502.5</v>
+      </c>
+      <c r="U258" t="n">
+        <v>492.5</v>
+      </c>
+      <c r="V258" t="n">
+        <v>493.92</v>
+      </c>
+      <c r="W258" t="n">
+        <v>501.58</v>
+      </c>
+      <c r="X258" t="n">
+        <v>505.13</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>492.9</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="n">
+        <v>510</v>
+      </c>
+      <c r="D259" t="n">
+        <v>500</v>
+      </c>
+      <c r="E259" t="n">
+        <v>470</v>
+      </c>
+      <c r="F259" t="n">
+        <v>469.5</v>
+      </c>
+      <c r="G259" t="n">
+        <v>461.5</v>
+      </c>
+      <c r="H259" t="n">
+        <v>469</v>
+      </c>
+      <c r="I259" t="n">
+        <v>398.64</v>
+      </c>
+      <c r="J259" t="n">
+        <v>135.57</v>
+      </c>
+      <c r="K259" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="M259" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="N259" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="O259" t="n">
+        <v>39</v>
+      </c>
+      <c r="P259" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>100</v>
+      </c>
+      <c r="R259" t="n">
+        <v>309</v>
+      </c>
+      <c r="S259" t="n">
+        <v>431.97</v>
+      </c>
+      <c r="T259" t="n">
+        <v>510</v>
+      </c>
+      <c r="U259" t="n">
+        <v>515.41</v>
+      </c>
+      <c r="V259" t="n">
+        <v>490</v>
+      </c>
+      <c r="W259" t="n">
+        <v>489.36</v>
+      </c>
+      <c r="X259" t="n">
+        <v>486.71</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>470.39</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>467.5</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" t="n">
+        <v>462.8</v>
+      </c>
+      <c r="D260" t="n">
+        <v>450</v>
+      </c>
+      <c r="E260" t="n">
+        <v>429</v>
+      </c>
+      <c r="F260" t="n">
+        <v>424.55</v>
+      </c>
+      <c r="G260" t="n">
+        <v>429.55</v>
+      </c>
+      <c r="H260" t="n">
+        <v>444.5</v>
+      </c>
+      <c r="I260" t="n">
+        <v>402.23</v>
+      </c>
+      <c r="J260" t="n">
+        <v>281.05</v>
+      </c>
+      <c r="K260" t="n">
+        <v>230</v>
+      </c>
+      <c r="L260" t="n">
+        <v>187.81</v>
+      </c>
+      <c r="M260" t="n">
+        <v>210</v>
+      </c>
+      <c r="N260" t="n">
+        <v>218.3</v>
+      </c>
+      <c r="O260" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="P260" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>319.5</v>
+      </c>
+      <c r="R260" t="n">
+        <v>389.75</v>
+      </c>
+      <c r="S260" t="n">
+        <v>504.87</v>
+      </c>
+      <c r="T260" t="n">
+        <v>540.35</v>
+      </c>
+      <c r="U260" t="n">
+        <v>529.38</v>
+      </c>
+      <c r="V260" t="n">
+        <v>515.6</v>
+      </c>
+      <c r="W260" t="n">
+        <v>510.74</v>
+      </c>
+      <c r="X260" t="n">
+        <v>512.8</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>528.63</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>527.26</v>
       </c>
     </row>
   </sheetData>

--- a/excel/2026/日前现货_发电侧小时电价.xlsx
+++ b/excel/2026/日前现货_发电侧小时电价.xlsx
@@ -1194,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z267"/>
+  <dimension ref="A1:Z276"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
@@ -22500,6 +22500,699 @@
         <v>465</v>
       </c>
     </row>
+    <row r="268" spans="1:26">
+      <c r="A268" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C268">
+        <v>481.81</v>
+      </c>
+      <c r="D268">
+        <v>469</v>
+      </c>
+      <c r="E268">
+        <v>434.24</v>
+      </c>
+      <c r="F268">
+        <v>435.15</v>
+      </c>
+      <c r="G268">
+        <v>430</v>
+      </c>
+      <c r="H268">
+        <v>445.79</v>
+      </c>
+      <c r="I268">
+        <v>404.38</v>
+      </c>
+      <c r="J268">
+        <v>226.32</v>
+      </c>
+      <c r="K268">
+        <v>49.5</v>
+      </c>
+      <c r="L268">
+        <v>11.5</v>
+      </c>
+      <c r="M268">
+        <v>1</v>
+      </c>
+      <c r="N268">
+        <v>0</v>
+      </c>
+      <c r="O268">
+        <v>0</v>
+      </c>
+      <c r="P268">
+        <v>19.5</v>
+      </c>
+      <c r="Q268">
+        <v>57.21</v>
+      </c>
+      <c r="R268">
+        <v>268.43</v>
+      </c>
+      <c r="S268">
+        <v>446.61</v>
+      </c>
+      <c r="T268">
+        <v>520.5</v>
+      </c>
+      <c r="U268">
+        <v>520.9</v>
+      </c>
+      <c r="V268">
+        <v>520.9</v>
+      </c>
+      <c r="W268">
+        <v>522.5</v>
+      </c>
+      <c r="X268">
+        <v>522.5</v>
+      </c>
+      <c r="Y268">
+        <v>522.64</v>
+      </c>
+      <c r="Z268">
+        <v>520.66</v>
+      </c>
+    </row>
+    <row r="269" spans="1:26">
+      <c r="A269" s="2">
+        <v>46296</v>
+      </c>
+      <c r="C269">
+        <v>520.5</v>
+      </c>
+      <c r="D269">
+        <v>509.2</v>
+      </c>
+      <c r="E269">
+        <v>502</v>
+      </c>
+      <c r="F269">
+        <v>500</v>
+      </c>
+      <c r="G269">
+        <v>500</v>
+      </c>
+      <c r="H269">
+        <v>500.57</v>
+      </c>
+      <c r="I269">
+        <v>425</v>
+      </c>
+      <c r="J269">
+        <v>200</v>
+      </c>
+      <c r="K269">
+        <v>-15</v>
+      </c>
+      <c r="L269">
+        <v>-30</v>
+      </c>
+      <c r="M269">
+        <v>-39.5</v>
+      </c>
+      <c r="N269">
+        <v>-30</v>
+      </c>
+      <c r="O269">
+        <v>-30</v>
+      </c>
+      <c r="P269">
+        <v>-30</v>
+      </c>
+      <c r="Q269">
+        <v>-19.5</v>
+      </c>
+      <c r="R269">
+        <v>199.5</v>
+      </c>
+      <c r="S269">
+        <v>473.1</v>
+      </c>
+      <c r="T269">
+        <v>511</v>
+      </c>
+      <c r="U269">
+        <v>507.18</v>
+      </c>
+      <c r="V269">
+        <v>500</v>
+      </c>
+      <c r="W269">
+        <v>492</v>
+      </c>
+      <c r="X269">
+        <v>481</v>
+      </c>
+      <c r="Y269">
+        <v>477.77</v>
+      </c>
+      <c r="Z269">
+        <v>478.06</v>
+      </c>
+    </row>
+    <row r="270" spans="1:26">
+      <c r="A270" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C270">
+        <v>486.15</v>
+      </c>
+      <c r="D270">
+        <v>473</v>
+      </c>
+      <c r="E270">
+        <v>465.5</v>
+      </c>
+      <c r="F270">
+        <v>464</v>
+      </c>
+      <c r="G270">
+        <v>466</v>
+      </c>
+      <c r="H270">
+        <v>458</v>
+      </c>
+      <c r="I270">
+        <v>450</v>
+      </c>
+      <c r="J270">
+        <v>364.9</v>
+      </c>
+      <c r="K270">
+        <v>356.25</v>
+      </c>
+      <c r="L270">
+        <v>331.77</v>
+      </c>
+      <c r="M270">
+        <v>312</v>
+      </c>
+      <c r="N270">
+        <v>302</v>
+      </c>
+      <c r="O270">
+        <v>298.58</v>
+      </c>
+      <c r="P270">
+        <v>298.35</v>
+      </c>
+      <c r="Q270">
+        <v>309</v>
+      </c>
+      <c r="R270">
+        <v>357.95</v>
+      </c>
+      <c r="S270">
+        <v>418.28</v>
+      </c>
+      <c r="T270">
+        <v>450</v>
+      </c>
+      <c r="U270">
+        <v>454.3</v>
+      </c>
+      <c r="V270">
+        <v>450</v>
+      </c>
+      <c r="W270">
+        <v>450</v>
+      </c>
+      <c r="X270">
+        <v>454.36</v>
+      </c>
+      <c r="Y270">
+        <v>459.45</v>
+      </c>
+      <c r="Z270">
+        <v>461.02</v>
+      </c>
+    </row>
+    <row r="271" spans="1:26">
+      <c r="A271" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C271">
+        <v>483.02</v>
+      </c>
+      <c r="D271">
+        <v>483</v>
+      </c>
+      <c r="E271">
+        <v>460</v>
+      </c>
+      <c r="F271">
+        <v>444</v>
+      </c>
+      <c r="G271">
+        <v>439.5</v>
+      </c>
+      <c r="H271">
+        <v>439.5</v>
+      </c>
+      <c r="I271">
+        <v>350.6</v>
+      </c>
+      <c r="J271">
+        <v>78.5</v>
+      </c>
+      <c r="K271">
+        <v>-50</v>
+      </c>
+      <c r="L271">
+        <v>-50</v>
+      </c>
+      <c r="M271">
+        <v>-60</v>
+      </c>
+      <c r="N271">
+        <v>-50</v>
+      </c>
+      <c r="O271">
+        <v>-60</v>
+      </c>
+      <c r="P271">
+        <v>-50</v>
+      </c>
+      <c r="Q271">
+        <v>-50</v>
+      </c>
+      <c r="R271">
+        <v>55.79</v>
+      </c>
+      <c r="S271">
+        <v>342.5</v>
+      </c>
+      <c r="T271">
+        <v>469.35</v>
+      </c>
+      <c r="U271">
+        <v>466.64</v>
+      </c>
+      <c r="V271">
+        <v>473.75</v>
+      </c>
+      <c r="W271">
+        <v>474.5</v>
+      </c>
+      <c r="X271">
+        <v>490.45</v>
+      </c>
+      <c r="Y271">
+        <v>497</v>
+      </c>
+      <c r="Z271">
+        <v>495.97</v>
+      </c>
+    </row>
+    <row r="272" spans="1:26">
+      <c r="A272" s="2">
+        <v>46299</v>
+      </c>
+      <c r="C272">
+        <v>500</v>
+      </c>
+      <c r="D272">
+        <v>494</v>
+      </c>
+      <c r="E272">
+        <v>480.6</v>
+      </c>
+      <c r="F272">
+        <v>451.54</v>
+      </c>
+      <c r="G272">
+        <v>442.33</v>
+      </c>
+      <c r="H272">
+        <v>453.5</v>
+      </c>
+      <c r="I272">
+        <v>415.3</v>
+      </c>
+      <c r="J272">
+        <v>100.5</v>
+      </c>
+      <c r="K272">
+        <v>-50</v>
+      </c>
+      <c r="L272">
+        <v>-65</v>
+      </c>
+      <c r="M272">
+        <v>-65</v>
+      </c>
+      <c r="N272">
+        <v>-69</v>
+      </c>
+      <c r="O272">
+        <v>-69</v>
+      </c>
+      <c r="P272">
+        <v>-70</v>
+      </c>
+      <c r="Q272">
+        <v>-50</v>
+      </c>
+      <c r="R272">
+        <v>29.5</v>
+      </c>
+      <c r="S272">
+        <v>423.5</v>
+      </c>
+      <c r="T272">
+        <v>524.15</v>
+      </c>
+      <c r="U272">
+        <v>550.5</v>
+      </c>
+      <c r="V272">
+        <v>550.5</v>
+      </c>
+      <c r="W272">
+        <v>552.5700000000001</v>
+      </c>
+      <c r="X272">
+        <v>533</v>
+      </c>
+      <c r="Y272">
+        <v>526.6799999999999</v>
+      </c>
+      <c r="Z272">
+        <v>507.5</v>
+      </c>
+    </row>
+    <row r="273" spans="1:26">
+      <c r="A273" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C273">
+        <v>548.5</v>
+      </c>
+      <c r="D273">
+        <v>522.5</v>
+      </c>
+      <c r="E273">
+        <v>502.5</v>
+      </c>
+      <c r="F273">
+        <v>490.3</v>
+      </c>
+      <c r="G273">
+        <v>498.94</v>
+      </c>
+      <c r="H273">
+        <v>504</v>
+      </c>
+      <c r="I273">
+        <v>484.3</v>
+      </c>
+      <c r="J273">
+        <v>233.25</v>
+      </c>
+      <c r="K273">
+        <v>-47</v>
+      </c>
+      <c r="L273">
+        <v>-50</v>
+      </c>
+      <c r="M273">
+        <v>-70</v>
+      </c>
+      <c r="N273">
+        <v>-70</v>
+      </c>
+      <c r="O273">
+        <v>-70</v>
+      </c>
+      <c r="P273">
+        <v>-63.5</v>
+      </c>
+      <c r="Q273">
+        <v>-26.02</v>
+      </c>
+      <c r="R273">
+        <v>238.3</v>
+      </c>
+      <c r="S273">
+        <v>471.4</v>
+      </c>
+      <c r="T273">
+        <v>564.66</v>
+      </c>
+      <c r="U273">
+        <v>569</v>
+      </c>
+      <c r="V273">
+        <v>568.4400000000001</v>
+      </c>
+      <c r="W273">
+        <v>571.45</v>
+      </c>
+      <c r="X273">
+        <v>572.01</v>
+      </c>
+      <c r="Y273">
+        <v>580</v>
+      </c>
+      <c r="Z273">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="274" spans="1:26">
+      <c r="A274" s="2">
+        <v>46301</v>
+      </c>
+      <c r="C274">
+        <v>566</v>
+      </c>
+      <c r="D274">
+        <v>559.95</v>
+      </c>
+      <c r="E274">
+        <v>549</v>
+      </c>
+      <c r="F274">
+        <v>549.5</v>
+      </c>
+      <c r="G274">
+        <v>560</v>
+      </c>
+      <c r="H274">
+        <v>560</v>
+      </c>
+      <c r="I274">
+        <v>531</v>
+      </c>
+      <c r="J274">
+        <v>430.4</v>
+      </c>
+      <c r="K274">
+        <v>151</v>
+      </c>
+      <c r="L274">
+        <v>5</v>
+      </c>
+      <c r="M274">
+        <v>-57.5</v>
+      </c>
+      <c r="N274">
+        <v>-10</v>
+      </c>
+      <c r="O274">
+        <v>-31.55</v>
+      </c>
+      <c r="P274">
+        <v>-53.59</v>
+      </c>
+      <c r="Q274">
+        <v>22.03</v>
+      </c>
+      <c r="R274">
+        <v>305.5</v>
+      </c>
+      <c r="S274">
+        <v>535</v>
+      </c>
+      <c r="T274">
+        <v>560.41</v>
+      </c>
+      <c r="U274">
+        <v>551</v>
+      </c>
+      <c r="V274">
+        <v>524</v>
+      </c>
+      <c r="W274">
+        <v>509.5</v>
+      </c>
+      <c r="X274">
+        <v>497.5</v>
+      </c>
+      <c r="Y274">
+        <v>484.55</v>
+      </c>
+      <c r="Z274">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="275" spans="1:26">
+      <c r="A275" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C275">
+        <v>447.95</v>
+      </c>
+      <c r="D275">
+        <v>427.5</v>
+      </c>
+      <c r="E275">
+        <v>420</v>
+      </c>
+      <c r="F275">
+        <v>428.5</v>
+      </c>
+      <c r="G275">
+        <v>446.6</v>
+      </c>
+      <c r="H275">
+        <v>496</v>
+      </c>
+      <c r="I275">
+        <v>471.2</v>
+      </c>
+      <c r="J275">
+        <v>251.82</v>
+      </c>
+      <c r="K275">
+        <v>28.9</v>
+      </c>
+      <c r="L275">
+        <v>0</v>
+      </c>
+      <c r="M275">
+        <v>0</v>
+      </c>
+      <c r="N275">
+        <v>18.4</v>
+      </c>
+      <c r="O275">
+        <v>20.3</v>
+      </c>
+      <c r="P275">
+        <v>22.5</v>
+      </c>
+      <c r="Q275">
+        <v>139.83</v>
+      </c>
+      <c r="R275">
+        <v>339.55</v>
+      </c>
+      <c r="S275">
+        <v>528.05</v>
+      </c>
+      <c r="T275">
+        <v>560</v>
+      </c>
+      <c r="U275">
+        <v>550</v>
+      </c>
+      <c r="V275">
+        <v>530</v>
+      </c>
+      <c r="W275">
+        <v>521.5</v>
+      </c>
+      <c r="X275">
+        <v>515.5</v>
+      </c>
+      <c r="Y275">
+        <v>530.76</v>
+      </c>
+      <c r="Z275">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="276" spans="1:26">
+      <c r="A276" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C276">
+        <v>500</v>
+      </c>
+      <c r="D276">
+        <v>498.5</v>
+      </c>
+      <c r="E276">
+        <v>494.5</v>
+      </c>
+      <c r="F276">
+        <v>500</v>
+      </c>
+      <c r="G276">
+        <v>507.32</v>
+      </c>
+      <c r="H276">
+        <v>533</v>
+      </c>
+      <c r="I276">
+        <v>531.02</v>
+      </c>
+      <c r="J276">
+        <v>392.1</v>
+      </c>
+      <c r="K276">
+        <v>227.19</v>
+      </c>
+      <c r="L276">
+        <v>79.05</v>
+      </c>
+      <c r="M276">
+        <v>-10</v>
+      </c>
+      <c r="N276">
+        <v>-10</v>
+      </c>
+      <c r="O276">
+        <v>-10</v>
+      </c>
+      <c r="P276">
+        <v>159</v>
+      </c>
+      <c r="Q276">
+        <v>236.85</v>
+      </c>
+      <c r="R276">
+        <v>401.35</v>
+      </c>
+      <c r="S276">
+        <v>541</v>
+      </c>
+      <c r="T276">
+        <v>557.5</v>
+      </c>
+      <c r="U276">
+        <v>554.05</v>
+      </c>
+      <c r="V276">
+        <v>550</v>
+      </c>
+      <c r="W276">
+        <v>550</v>
+      </c>
+      <c r="X276">
+        <v>530</v>
+      </c>
+      <c r="Y276">
+        <v>535</v>
+      </c>
+      <c r="Z276">
+        <v>543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel/2026/日前现货_发电侧小时电价.xlsx
+++ b/excel/2026/日前现货_发电侧小时电价.xlsx
@@ -1194,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z276"/>
+  <dimension ref="A1:Z283"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
@@ -22502,694 +22502,1233 @@
     </row>
     <row r="268" spans="1:26">
       <c r="A268" s="2">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="C268">
-        <v>481.81</v>
+        <v>460</v>
       </c>
       <c r="D268">
+        <v>462.66</v>
+      </c>
+      <c r="E268">
+        <v>447.45</v>
+      </c>
+      <c r="F268">
+        <v>450</v>
+      </c>
+      <c r="G268">
+        <v>460.64</v>
+      </c>
+      <c r="H268">
+        <v>458.73</v>
+      </c>
+      <c r="I268">
+        <v>465.98</v>
+      </c>
+      <c r="J268">
+        <v>455</v>
+      </c>
+      <c r="K268">
+        <v>461</v>
+      </c>
+      <c r="L268">
+        <v>470.45</v>
+      </c>
+      <c r="M268">
         <v>469</v>
       </c>
-      <c r="E268">
-        <v>434.24</v>
-      </c>
-      <c r="F268">
-        <v>435.15</v>
-      </c>
-      <c r="G268">
-        <v>430</v>
-      </c>
-      <c r="H268">
-        <v>445.79</v>
-      </c>
-      <c r="I268">
-        <v>404.38</v>
-      </c>
-      <c r="J268">
-        <v>226.32</v>
-      </c>
-      <c r="K268">
-        <v>49.5</v>
-      </c>
-      <c r="L268">
-        <v>11.5</v>
-      </c>
-      <c r="M268">
-        <v>1</v>
-      </c>
       <c r="N268">
-        <v>0</v>
+        <v>470.5</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>459.5</v>
       </c>
       <c r="P268">
-        <v>19.5</v>
+        <v>462.6</v>
       </c>
       <c r="Q268">
-        <v>57.21</v>
+        <v>471</v>
       </c>
       <c r="R268">
-        <v>268.43</v>
+        <v>488.9</v>
       </c>
       <c r="S268">
-        <v>446.61</v>
+        <v>497.4</v>
       </c>
       <c r="T268">
-        <v>520.5</v>
+        <v>469.5</v>
       </c>
       <c r="U268">
-        <v>520.9</v>
+        <v>469.5</v>
       </c>
       <c r="V268">
-        <v>520.9</v>
+        <v>460</v>
       </c>
       <c r="W268">
-        <v>522.5</v>
+        <v>458.72</v>
       </c>
       <c r="X268">
-        <v>522.5</v>
+        <v>457</v>
       </c>
       <c r="Y268">
-        <v>522.64</v>
+        <v>458</v>
       </c>
       <c r="Z268">
-        <v>520.66</v>
+        <v>459.5</v>
       </c>
     </row>
     <row r="269" spans="1:26">
       <c r="A269" s="2">
-        <v>46296</v>
+        <v>46289</v>
       </c>
       <c r="C269">
-        <v>520.5</v>
+        <v>460</v>
       </c>
       <c r="D269">
-        <v>509.2</v>
+        <v>460</v>
       </c>
       <c r="E269">
-        <v>502</v>
+        <v>468.63</v>
       </c>
       <c r="F269">
-        <v>500</v>
+        <v>465.9</v>
       </c>
       <c r="G269">
-        <v>500</v>
+        <v>465</v>
       </c>
       <c r="H269">
-        <v>500.57</v>
+        <v>454.73</v>
       </c>
       <c r="I269">
-        <v>425</v>
+        <v>439.61</v>
       </c>
       <c r="J269">
-        <v>200</v>
+        <v>443.59</v>
       </c>
       <c r="K269">
-        <v>-15</v>
+        <v>451.5</v>
       </c>
       <c r="L269">
-        <v>-30</v>
+        <v>455.85</v>
       </c>
       <c r="M269">
-        <v>-39.5</v>
+        <v>464.45</v>
       </c>
       <c r="N269">
-        <v>-30</v>
+        <v>460.48</v>
       </c>
       <c r="O269">
-        <v>-30</v>
+        <v>437.44</v>
       </c>
       <c r="P269">
-        <v>-30</v>
+        <v>438.37</v>
       </c>
       <c r="Q269">
-        <v>-19.5</v>
+        <v>442.74</v>
       </c>
       <c r="R269">
-        <v>199.5</v>
+        <v>460.5</v>
       </c>
       <c r="S269">
-        <v>473.1</v>
+        <v>463.65</v>
       </c>
       <c r="T269">
-        <v>511</v>
+        <v>469</v>
       </c>
       <c r="U269">
-        <v>507.18</v>
+        <v>472</v>
       </c>
       <c r="V269">
-        <v>500</v>
+        <v>475.68</v>
       </c>
       <c r="W269">
-        <v>492</v>
+        <v>481.5</v>
       </c>
       <c r="X269">
-        <v>481</v>
+        <v>467.5</v>
       </c>
       <c r="Y269">
-        <v>477.77</v>
+        <v>467</v>
       </c>
       <c r="Z269">
-        <v>478.06</v>
+        <v>465</v>
       </c>
     </row>
     <row r="270" spans="1:26">
       <c r="A270" s="2">
-        <v>46297</v>
+        <v>46290</v>
       </c>
       <c r="C270">
-        <v>486.15</v>
+        <v>457.5</v>
       </c>
       <c r="D270">
-        <v>473</v>
+        <v>450</v>
       </c>
       <c r="E270">
-        <v>465.5</v>
+        <v>443.86</v>
       </c>
       <c r="F270">
-        <v>464</v>
+        <v>437.5</v>
       </c>
       <c r="G270">
-        <v>466</v>
+        <v>436.5</v>
       </c>
       <c r="H270">
-        <v>458</v>
+        <v>442.5</v>
       </c>
       <c r="I270">
-        <v>450</v>
+        <v>429.9</v>
       </c>
       <c r="J270">
-        <v>364.9</v>
+        <v>342.75</v>
       </c>
       <c r="K270">
-        <v>356.25</v>
+        <v>292.59</v>
       </c>
       <c r="L270">
-        <v>331.77</v>
+        <v>241.51</v>
       </c>
       <c r="M270">
-        <v>312</v>
+        <v>235.44</v>
       </c>
       <c r="N270">
-        <v>302</v>
+        <v>227.63</v>
       </c>
       <c r="O270">
-        <v>298.58</v>
+        <v>260</v>
       </c>
       <c r="P270">
-        <v>298.35</v>
+        <v>292.2</v>
       </c>
       <c r="Q270">
-        <v>309</v>
+        <v>349.91</v>
       </c>
       <c r="R270">
-        <v>357.95</v>
+        <v>427.05</v>
       </c>
       <c r="S270">
-        <v>418.28</v>
+        <v>452.28</v>
       </c>
       <c r="T270">
-        <v>450</v>
+        <v>494.55</v>
       </c>
       <c r="U270">
-        <v>454.3</v>
+        <v>493.49</v>
       </c>
       <c r="V270">
-        <v>450</v>
+        <v>481.62</v>
       </c>
       <c r="W270">
-        <v>450</v>
+        <v>472.45</v>
       </c>
       <c r="X270">
-        <v>454.36</v>
+        <v>468.59</v>
       </c>
       <c r="Y270">
-        <v>459.45</v>
+        <v>465.23</v>
       </c>
       <c r="Z270">
-        <v>461.02</v>
+        <v>463.03</v>
       </c>
     </row>
     <row r="271" spans="1:26">
       <c r="A271" s="2">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C271">
-        <v>483.02</v>
+        <v>450.5</v>
       </c>
       <c r="D271">
-        <v>483</v>
+        <v>448.5</v>
       </c>
       <c r="E271">
-        <v>460</v>
+        <v>437.9</v>
       </c>
       <c r="F271">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="G271">
-        <v>439.5</v>
+        <v>434</v>
       </c>
       <c r="H271">
-        <v>439.5</v>
+        <v>439.55</v>
       </c>
       <c r="I271">
-        <v>350.6</v>
+        <v>439.4</v>
       </c>
       <c r="J271">
-        <v>78.5</v>
+        <v>428.4</v>
       </c>
       <c r="K271">
-        <v>-50</v>
+        <v>416.2</v>
       </c>
       <c r="L271">
-        <v>-50</v>
+        <v>401.7</v>
       </c>
       <c r="M271">
-        <v>-60</v>
+        <v>419.7</v>
       </c>
       <c r="N271">
-        <v>-50</v>
+        <v>424.2</v>
       </c>
       <c r="O271">
-        <v>-60</v>
+        <v>402.53</v>
       </c>
       <c r="P271">
-        <v>-50</v>
+        <v>431.9</v>
       </c>
       <c r="Q271">
-        <v>-50</v>
+        <v>451</v>
       </c>
       <c r="R271">
-        <v>55.79</v>
+        <v>466.5</v>
       </c>
       <c r="S271">
-        <v>342.5</v>
+        <v>491.77</v>
       </c>
       <c r="T271">
-        <v>469.35</v>
+        <v>484.85</v>
       </c>
       <c r="U271">
-        <v>466.64</v>
+        <v>480.82</v>
       </c>
       <c r="V271">
-        <v>473.75</v>
+        <v>475.18</v>
       </c>
       <c r="W271">
-        <v>474.5</v>
+        <v>478.75</v>
       </c>
       <c r="X271">
-        <v>490.45</v>
+        <v>479.17</v>
       </c>
       <c r="Y271">
-        <v>497</v>
+        <v>469.63</v>
       </c>
       <c r="Z271">
-        <v>495.97</v>
+        <v>468.5</v>
       </c>
     </row>
     <row r="272" spans="1:26">
       <c r="A272" s="2">
-        <v>46299</v>
+        <v>46292</v>
       </c>
       <c r="C272">
-        <v>500</v>
+        <v>464.99</v>
       </c>
       <c r="D272">
-        <v>494</v>
+        <v>453.16</v>
       </c>
       <c r="E272">
-        <v>480.6</v>
+        <v>450</v>
       </c>
       <c r="F272">
-        <v>451.54</v>
+        <v>450</v>
       </c>
       <c r="G272">
-        <v>442.33</v>
+        <v>446.5</v>
       </c>
       <c r="H272">
-        <v>453.5</v>
+        <v>450</v>
       </c>
       <c r="I272">
-        <v>415.3</v>
+        <v>425.48</v>
       </c>
       <c r="J272">
-        <v>100.5</v>
+        <v>425.81</v>
       </c>
       <c r="K272">
-        <v>-50</v>
+        <v>430</v>
       </c>
       <c r="L272">
-        <v>-65</v>
+        <v>415.7</v>
       </c>
       <c r="M272">
-        <v>-65</v>
+        <v>437.05</v>
       </c>
       <c r="N272">
-        <v>-69</v>
+        <v>446.81</v>
       </c>
       <c r="O272">
-        <v>-69</v>
+        <v>436.5</v>
       </c>
       <c r="P272">
-        <v>-70</v>
+        <v>452.68</v>
       </c>
       <c r="Q272">
-        <v>-50</v>
+        <v>462.18</v>
       </c>
       <c r="R272">
-        <v>29.5</v>
+        <v>480</v>
       </c>
       <c r="S272">
-        <v>423.5</v>
+        <v>480</v>
       </c>
       <c r="T272">
-        <v>524.15</v>
+        <v>467</v>
       </c>
       <c r="U272">
-        <v>550.5</v>
+        <v>461.43</v>
       </c>
       <c r="V272">
-        <v>550.5</v>
+        <v>466.5</v>
       </c>
       <c r="W272">
-        <v>552.5700000000001</v>
+        <v>458.54</v>
       </c>
       <c r="X272">
-        <v>533</v>
+        <v>458.6</v>
       </c>
       <c r="Y272">
-        <v>526.6799999999999</v>
+        <v>458</v>
       </c>
       <c r="Z272">
-        <v>507.5</v>
+        <v>460</v>
       </c>
     </row>
     <row r="273" spans="1:26">
       <c r="A273" s="2">
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="C273">
-        <v>548.5</v>
+        <v>460.95</v>
       </c>
       <c r="D273">
-        <v>522.5</v>
+        <v>450</v>
       </c>
       <c r="E273">
-        <v>502.5</v>
+        <v>448.5</v>
       </c>
       <c r="F273">
-        <v>490.3</v>
+        <v>438.9</v>
       </c>
       <c r="G273">
-        <v>498.94</v>
+        <v>439.4</v>
       </c>
       <c r="H273">
-        <v>504</v>
+        <v>445.15</v>
       </c>
       <c r="I273">
-        <v>484.3</v>
+        <v>434.35</v>
       </c>
       <c r="J273">
-        <v>233.25</v>
+        <v>400</v>
       </c>
       <c r="K273">
-        <v>-47</v>
+        <v>340.3</v>
       </c>
       <c r="L273">
-        <v>-50</v>
+        <v>280</v>
       </c>
       <c r="M273">
-        <v>-70</v>
+        <v>300.5</v>
       </c>
       <c r="N273">
-        <v>-70</v>
+        <v>300</v>
       </c>
       <c r="O273">
-        <v>-70</v>
+        <v>255.5</v>
       </c>
       <c r="P273">
-        <v>-63.5</v>
+        <v>299.4</v>
       </c>
       <c r="Q273">
-        <v>-26.02</v>
+        <v>378.73</v>
       </c>
       <c r="R273">
-        <v>238.3</v>
+        <v>429</v>
       </c>
       <c r="S273">
-        <v>471.4</v>
+        <v>452.91</v>
       </c>
       <c r="T273">
-        <v>564.66</v>
+        <v>471</v>
       </c>
       <c r="U273">
-        <v>569</v>
+        <v>467.68</v>
       </c>
       <c r="V273">
-        <v>568.4400000000001</v>
+        <v>450.5</v>
       </c>
       <c r="W273">
-        <v>571.45</v>
+        <v>450</v>
       </c>
       <c r="X273">
-        <v>572.01</v>
+        <v>451.66</v>
       </c>
       <c r="Y273">
-        <v>580</v>
+        <v>439.65</v>
       </c>
       <c r="Z273">
-        <v>580</v>
+        <v>429</v>
       </c>
     </row>
     <row r="274" spans="1:26">
       <c r="A274" s="2">
-        <v>46301</v>
+        <v>46294</v>
       </c>
       <c r="C274">
-        <v>566</v>
+        <v>418.8</v>
       </c>
       <c r="D274">
-        <v>559.95</v>
+        <v>420</v>
       </c>
       <c r="E274">
-        <v>549</v>
+        <v>413.5</v>
       </c>
       <c r="F274">
-        <v>549.5</v>
+        <v>414.36</v>
       </c>
       <c r="G274">
-        <v>560</v>
+        <v>420</v>
       </c>
       <c r="H274">
-        <v>560</v>
+        <v>417.05</v>
       </c>
       <c r="I274">
-        <v>531</v>
+        <v>419.5</v>
       </c>
       <c r="J274">
-        <v>430.4</v>
+        <v>397.31</v>
       </c>
       <c r="K274">
-        <v>151</v>
+        <v>390.5</v>
       </c>
       <c r="L274">
-        <v>5</v>
+        <v>362.57</v>
       </c>
       <c r="M274">
-        <v>-57.5</v>
+        <v>236</v>
       </c>
       <c r="N274">
-        <v>-10</v>
+        <v>219.27</v>
       </c>
       <c r="O274">
-        <v>-31.55</v>
+        <v>210.25</v>
       </c>
       <c r="P274">
-        <v>-53.59</v>
+        <v>248.4</v>
       </c>
       <c r="Q274">
-        <v>22.03</v>
+        <v>306.95</v>
       </c>
       <c r="R274">
-        <v>305.5</v>
+        <v>328.76</v>
       </c>
       <c r="S274">
-        <v>535</v>
+        <v>390.56</v>
       </c>
       <c r="T274">
-        <v>560.41</v>
+        <v>415</v>
       </c>
       <c r="U274">
-        <v>551</v>
+        <v>415</v>
       </c>
       <c r="V274">
-        <v>524</v>
+        <v>415.5</v>
       </c>
       <c r="W274">
-        <v>509.5</v>
+        <v>425.5</v>
       </c>
       <c r="X274">
-        <v>497.5</v>
+        <v>439.63</v>
       </c>
       <c r="Y274">
-        <v>484.55</v>
+        <v>439.86</v>
       </c>
       <c r="Z274">
-        <v>480</v>
+        <v>433.75</v>
       </c>
     </row>
     <row r="275" spans="1:26">
       <c r="A275" s="2">
-        <v>46302</v>
+        <v>46295</v>
       </c>
       <c r="C275">
-        <v>447.95</v>
+        <v>481.81</v>
       </c>
       <c r="D275">
-        <v>427.5</v>
+        <v>469</v>
       </c>
       <c r="E275">
-        <v>420</v>
+        <v>434.24</v>
       </c>
       <c r="F275">
-        <v>428.5</v>
+        <v>435.15</v>
       </c>
       <c r="G275">
-        <v>446.6</v>
+        <v>430</v>
       </c>
       <c r="H275">
-        <v>496</v>
+        <v>445.79</v>
       </c>
       <c r="I275">
-        <v>471.2</v>
+        <v>404.38</v>
       </c>
       <c r="J275">
-        <v>251.82</v>
+        <v>226.32</v>
       </c>
       <c r="K275">
-        <v>28.9</v>
+        <v>49.5</v>
       </c>
       <c r="L275">
+        <v>11.5</v>
+      </c>
+      <c r="M275">
+        <v>1</v>
+      </c>
+      <c r="N275">
         <v>0</v>
       </c>
-      <c r="M275">
+      <c r="O275">
         <v>0</v>
       </c>
-      <c r="N275">
-        <v>18.4</v>
-      </c>
-      <c r="O275">
-        <v>20.3</v>
-      </c>
       <c r="P275">
-        <v>22.5</v>
+        <v>19.5</v>
       </c>
       <c r="Q275">
-        <v>139.83</v>
+        <v>57.21</v>
       </c>
       <c r="R275">
-        <v>339.55</v>
+        <v>268.43</v>
       </c>
       <c r="S275">
-        <v>528.05</v>
+        <v>446.61</v>
       </c>
       <c r="T275">
-        <v>560</v>
+        <v>520.5</v>
       </c>
       <c r="U275">
-        <v>550</v>
+        <v>520.9</v>
       </c>
       <c r="V275">
-        <v>530</v>
+        <v>520.9</v>
       </c>
       <c r="W275">
-        <v>521.5</v>
+        <v>522.5</v>
       </c>
       <c r="X275">
-        <v>515.5</v>
+        <v>522.5</v>
       </c>
       <c r="Y275">
-        <v>530.76</v>
+        <v>522.64</v>
       </c>
       <c r="Z275">
-        <v>530</v>
+        <v>520.66</v>
       </c>
     </row>
     <row r="276" spans="1:26">
       <c r="A276" s="2">
-        <v>46303</v>
+        <v>46296</v>
       </c>
       <c r="C276">
-        <v>500</v>
+        <v>520.5</v>
       </c>
       <c r="D276">
-        <v>498.5</v>
+        <v>509.2</v>
       </c>
       <c r="E276">
-        <v>494.5</v>
+        <v>502</v>
       </c>
       <c r="F276">
         <v>500</v>
       </c>
       <c r="G276">
+        <v>500</v>
+      </c>
+      <c r="H276">
+        <v>500.57</v>
+      </c>
+      <c r="I276">
+        <v>425</v>
+      </c>
+      <c r="J276">
+        <v>200</v>
+      </c>
+      <c r="K276">
+        <v>-15</v>
+      </c>
+      <c r="L276">
+        <v>-30</v>
+      </c>
+      <c r="M276">
+        <v>-39.5</v>
+      </c>
+      <c r="N276">
+        <v>-30</v>
+      </c>
+      <c r="O276">
+        <v>-30</v>
+      </c>
+      <c r="P276">
+        <v>-30</v>
+      </c>
+      <c r="Q276">
+        <v>-19.5</v>
+      </c>
+      <c r="R276">
+        <v>199.5</v>
+      </c>
+      <c r="S276">
+        <v>473.1</v>
+      </c>
+      <c r="T276">
+        <v>511</v>
+      </c>
+      <c r="U276">
+        <v>507.18</v>
+      </c>
+      <c r="V276">
+        <v>500</v>
+      </c>
+      <c r="W276">
+        <v>492</v>
+      </c>
+      <c r="X276">
+        <v>481</v>
+      </c>
+      <c r="Y276">
+        <v>477.77</v>
+      </c>
+      <c r="Z276">
+        <v>478.06</v>
+      </c>
+    </row>
+    <row r="277" spans="1:26">
+      <c r="A277" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C277">
+        <v>486.15</v>
+      </c>
+      <c r="D277">
+        <v>473</v>
+      </c>
+      <c r="E277">
+        <v>465.5</v>
+      </c>
+      <c r="F277">
+        <v>464</v>
+      </c>
+      <c r="G277">
+        <v>466</v>
+      </c>
+      <c r="H277">
+        <v>458</v>
+      </c>
+      <c r="I277">
+        <v>450</v>
+      </c>
+      <c r="J277">
+        <v>364.9</v>
+      </c>
+      <c r="K277">
+        <v>356.25</v>
+      </c>
+      <c r="L277">
+        <v>331.77</v>
+      </c>
+      <c r="M277">
+        <v>312</v>
+      </c>
+      <c r="N277">
+        <v>302</v>
+      </c>
+      <c r="O277">
+        <v>298.58</v>
+      </c>
+      <c r="P277">
+        <v>298.35</v>
+      </c>
+      <c r="Q277">
+        <v>309</v>
+      </c>
+      <c r="R277">
+        <v>357.95</v>
+      </c>
+      <c r="S277">
+        <v>418.28</v>
+      </c>
+      <c r="T277">
+        <v>450</v>
+      </c>
+      <c r="U277">
+        <v>454.3</v>
+      </c>
+      <c r="V277">
+        <v>450</v>
+      </c>
+      <c r="W277">
+        <v>450</v>
+      </c>
+      <c r="X277">
+        <v>454.36</v>
+      </c>
+      <c r="Y277">
+        <v>459.45</v>
+      </c>
+      <c r="Z277">
+        <v>461.02</v>
+      </c>
+    </row>
+    <row r="278" spans="1:26">
+      <c r="A278" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C278">
+        <v>483.02</v>
+      </c>
+      <c r="D278">
+        <v>483</v>
+      </c>
+      <c r="E278">
+        <v>460</v>
+      </c>
+      <c r="F278">
+        <v>444</v>
+      </c>
+      <c r="G278">
+        <v>439.5</v>
+      </c>
+      <c r="H278">
+        <v>439.5</v>
+      </c>
+      <c r="I278">
+        <v>350.6</v>
+      </c>
+      <c r="J278">
+        <v>78.5</v>
+      </c>
+      <c r="K278">
+        <v>-50</v>
+      </c>
+      <c r="L278">
+        <v>-50</v>
+      </c>
+      <c r="M278">
+        <v>-60</v>
+      </c>
+      <c r="N278">
+        <v>-50</v>
+      </c>
+      <c r="O278">
+        <v>-60</v>
+      </c>
+      <c r="P278">
+        <v>-50</v>
+      </c>
+      <c r="Q278">
+        <v>-50</v>
+      </c>
+      <c r="R278">
+        <v>55.79</v>
+      </c>
+      <c r="S278">
+        <v>342.5</v>
+      </c>
+      <c r="T278">
+        <v>469.35</v>
+      </c>
+      <c r="U278">
+        <v>466.64</v>
+      </c>
+      <c r="V278">
+        <v>473.75</v>
+      </c>
+      <c r="W278">
+        <v>474.5</v>
+      </c>
+      <c r="X278">
+        <v>490.45</v>
+      </c>
+      <c r="Y278">
+        <v>497</v>
+      </c>
+      <c r="Z278">
+        <v>495.97</v>
+      </c>
+    </row>
+    <row r="279" spans="1:26">
+      <c r="A279" s="2">
+        <v>46299</v>
+      </c>
+      <c r="C279">
+        <v>500</v>
+      </c>
+      <c r="D279">
+        <v>494</v>
+      </c>
+      <c r="E279">
+        <v>480.6</v>
+      </c>
+      <c r="F279">
+        <v>451.54</v>
+      </c>
+      <c r="G279">
+        <v>442.33</v>
+      </c>
+      <c r="H279">
+        <v>453.5</v>
+      </c>
+      <c r="I279">
+        <v>415.3</v>
+      </c>
+      <c r="J279">
+        <v>100.5</v>
+      </c>
+      <c r="K279">
+        <v>-50</v>
+      </c>
+      <c r="L279">
+        <v>-65</v>
+      </c>
+      <c r="M279">
+        <v>-65</v>
+      </c>
+      <c r="N279">
+        <v>-69</v>
+      </c>
+      <c r="O279">
+        <v>-69</v>
+      </c>
+      <c r="P279">
+        <v>-70</v>
+      </c>
+      <c r="Q279">
+        <v>-50</v>
+      </c>
+      <c r="R279">
+        <v>29.5</v>
+      </c>
+      <c r="S279">
+        <v>423.5</v>
+      </c>
+      <c r="T279">
+        <v>524.15</v>
+      </c>
+      <c r="U279">
+        <v>550.5</v>
+      </c>
+      <c r="V279">
+        <v>550.5</v>
+      </c>
+      <c r="W279">
+        <v>552.5700000000001</v>
+      </c>
+      <c r="X279">
+        <v>533</v>
+      </c>
+      <c r="Y279">
+        <v>526.6799999999999</v>
+      </c>
+      <c r="Z279">
+        <v>507.5</v>
+      </c>
+    </row>
+    <row r="280" spans="1:26">
+      <c r="A280" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C280">
+        <v>548.5</v>
+      </c>
+      <c r="D280">
+        <v>522.5</v>
+      </c>
+      <c r="E280">
+        <v>502.5</v>
+      </c>
+      <c r="F280">
+        <v>490.3</v>
+      </c>
+      <c r="G280">
+        <v>498.94</v>
+      </c>
+      <c r="H280">
+        <v>504</v>
+      </c>
+      <c r="I280">
+        <v>484.3</v>
+      </c>
+      <c r="J280">
+        <v>233.25</v>
+      </c>
+      <c r="K280">
+        <v>-47</v>
+      </c>
+      <c r="L280">
+        <v>-50</v>
+      </c>
+      <c r="M280">
+        <v>-70</v>
+      </c>
+      <c r="N280">
+        <v>-70</v>
+      </c>
+      <c r="O280">
+        <v>-70</v>
+      </c>
+      <c r="P280">
+        <v>-63.5</v>
+      </c>
+      <c r="Q280">
+        <v>-26.02</v>
+      </c>
+      <c r="R280">
+        <v>238.3</v>
+      </c>
+      <c r="S280">
+        <v>471.4</v>
+      </c>
+      <c r="T280">
+        <v>564.66</v>
+      </c>
+      <c r="U280">
+        <v>569</v>
+      </c>
+      <c r="V280">
+        <v>568.4400000000001</v>
+      </c>
+      <c r="W280">
+        <v>571.45</v>
+      </c>
+      <c r="X280">
+        <v>572.01</v>
+      </c>
+      <c r="Y280">
+        <v>580</v>
+      </c>
+      <c r="Z280">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="281" spans="1:26">
+      <c r="A281" s="2">
+        <v>46301</v>
+      </c>
+      <c r="C281">
+        <v>566</v>
+      </c>
+      <c r="D281">
+        <v>559.95</v>
+      </c>
+      <c r="E281">
+        <v>549</v>
+      </c>
+      <c r="F281">
+        <v>549.5</v>
+      </c>
+      <c r="G281">
+        <v>560</v>
+      </c>
+      <c r="H281">
+        <v>560</v>
+      </c>
+      <c r="I281">
+        <v>531</v>
+      </c>
+      <c r="J281">
+        <v>430.4</v>
+      </c>
+      <c r="K281">
+        <v>151</v>
+      </c>
+      <c r="L281">
+        <v>5</v>
+      </c>
+      <c r="M281">
+        <v>-57.5</v>
+      </c>
+      <c r="N281">
+        <v>-10</v>
+      </c>
+      <c r="O281">
+        <v>-31.55</v>
+      </c>
+      <c r="P281">
+        <v>-53.59</v>
+      </c>
+      <c r="Q281">
+        <v>22.03</v>
+      </c>
+      <c r="R281">
+        <v>305.5</v>
+      </c>
+      <c r="S281">
+        <v>535</v>
+      </c>
+      <c r="T281">
+        <v>560.41</v>
+      </c>
+      <c r="U281">
+        <v>551</v>
+      </c>
+      <c r="V281">
+        <v>524</v>
+      </c>
+      <c r="W281">
+        <v>509.5</v>
+      </c>
+      <c r="X281">
+        <v>497.5</v>
+      </c>
+      <c r="Y281">
+        <v>484.55</v>
+      </c>
+      <c r="Z281">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="282" spans="1:26">
+      <c r="A282" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C282">
+        <v>447.95</v>
+      </c>
+      <c r="D282">
+        <v>427.5</v>
+      </c>
+      <c r="E282">
+        <v>420</v>
+      </c>
+      <c r="F282">
+        <v>428.5</v>
+      </c>
+      <c r="G282">
+        <v>446.6</v>
+      </c>
+      <c r="H282">
+        <v>496</v>
+      </c>
+      <c r="I282">
+        <v>471.2</v>
+      </c>
+      <c r="J282">
+        <v>251.82</v>
+      </c>
+      <c r="K282">
+        <v>28.9</v>
+      </c>
+      <c r="L282">
+        <v>0</v>
+      </c>
+      <c r="M282">
+        <v>0</v>
+      </c>
+      <c r="N282">
+        <v>18.4</v>
+      </c>
+      <c r="O282">
+        <v>20.3</v>
+      </c>
+      <c r="P282">
+        <v>22.5</v>
+      </c>
+      <c r="Q282">
+        <v>139.83</v>
+      </c>
+      <c r="R282">
+        <v>339.55</v>
+      </c>
+      <c r="S282">
+        <v>528.05</v>
+      </c>
+      <c r="T282">
+        <v>560</v>
+      </c>
+      <c r="U282">
+        <v>550</v>
+      </c>
+      <c r="V282">
+        <v>530</v>
+      </c>
+      <c r="W282">
+        <v>521.5</v>
+      </c>
+      <c r="X282">
+        <v>515.5</v>
+      </c>
+      <c r="Y282">
+        <v>530.76</v>
+      </c>
+      <c r="Z282">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="283" spans="1:26">
+      <c r="A283" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C283">
+        <v>500</v>
+      </c>
+      <c r="D283">
+        <v>498.5</v>
+      </c>
+      <c r="E283">
+        <v>494.5</v>
+      </c>
+      <c r="F283">
+        <v>500</v>
+      </c>
+      <c r="G283">
         <v>507.32</v>
       </c>
-      <c r="H276">
+      <c r="H283">
         <v>533</v>
       </c>
-      <c r="I276">
+      <c r="I283">
         <v>531.02</v>
       </c>
-      <c r="J276">
+      <c r="J283">
         <v>392.1</v>
       </c>
-      <c r="K276">
+      <c r="K283">
         <v>227.19</v>
       </c>
-      <c r="L276">
+      <c r="L283">
         <v>79.05</v>
       </c>
-      <c r="M276">
+      <c r="M283">
         <v>-10</v>
       </c>
-      <c r="N276">
+      <c r="N283">
         <v>-10</v>
       </c>
-      <c r="O276">
+      <c r="O283">
         <v>-10</v>
       </c>
-      <c r="P276">
+      <c r="P283">
         <v>159</v>
       </c>
-      <c r="Q276">
+      <c r="Q283">
         <v>236.85</v>
       </c>
-      <c r="R276">
+      <c r="R283">
         <v>401.35</v>
       </c>
-      <c r="S276">
+      <c r="S283">
         <v>541</v>
       </c>
-      <c r="T276">
+      <c r="T283">
         <v>557.5</v>
       </c>
-      <c r="U276">
+      <c r="U283">
         <v>554.05</v>
       </c>
-      <c r="V276">
+      <c r="V283">
         <v>550</v>
       </c>
-      <c r="W276">
+      <c r="W283">
         <v>550</v>
       </c>
-      <c r="X276">
+      <c r="X283">
         <v>530</v>
       </c>
-      <c r="Y276">
+      <c r="Y283">
         <v>535</v>
       </c>
-      <c r="Z276">
+      <c r="Z283">
         <v>543</v>
       </c>
     </row>

--- a/excel/2026/日前现货_发电侧小时电价.xlsx
+++ b/excel/2026/日前现货_发电侧小时电价.xlsx
@@ -1194,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z283"/>
+  <dimension ref="A1:Z286"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
@@ -23732,6 +23732,237 @@
         <v>543</v>
       </c>
     </row>
+    <row r="284" spans="1:26">
+      <c r="A284" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C284">
+        <v>473.21</v>
+      </c>
+      <c r="D284">
+        <v>469.26</v>
+      </c>
+      <c r="E284">
+        <v>469.5</v>
+      </c>
+      <c r="F284">
+        <v>469.5</v>
+      </c>
+      <c r="G284">
+        <v>472.29</v>
+      </c>
+      <c r="H284">
+        <v>514.5</v>
+      </c>
+      <c r="I284">
+        <v>523.5</v>
+      </c>
+      <c r="J284">
+        <v>439.5</v>
+      </c>
+      <c r="K284">
+        <v>359.4</v>
+      </c>
+      <c r="L284">
+        <v>310</v>
+      </c>
+      <c r="M284">
+        <v>305.75</v>
+      </c>
+      <c r="N284">
+        <v>299.55</v>
+      </c>
+      <c r="O284">
+        <v>296.15</v>
+      </c>
+      <c r="P284">
+        <v>299.24</v>
+      </c>
+      <c r="Q284">
+        <v>369.5</v>
+      </c>
+      <c r="R284">
+        <v>434</v>
+      </c>
+      <c r="S284">
+        <v>534.85</v>
+      </c>
+      <c r="T284">
+        <v>550</v>
+      </c>
+      <c r="U284">
+        <v>548</v>
+      </c>
+      <c r="V284">
+        <v>538.4400000000001</v>
+      </c>
+      <c r="W284">
+        <v>527</v>
+      </c>
+      <c r="X284">
+        <v>524</v>
+      </c>
+      <c r="Y284">
+        <v>528</v>
+      </c>
+      <c r="Z284">
+        <v>527.9400000000001</v>
+      </c>
+    </row>
+    <row r="285" spans="1:26">
+      <c r="A285" s="2">
+        <v>46305</v>
+      </c>
+      <c r="C285">
+        <v>509</v>
+      </c>
+      <c r="D285">
+        <v>509</v>
+      </c>
+      <c r="E285">
+        <v>511.15</v>
+      </c>
+      <c r="F285">
+        <v>499.68</v>
+      </c>
+      <c r="G285">
+        <v>519.55</v>
+      </c>
+      <c r="H285">
+        <v>525</v>
+      </c>
+      <c r="I285">
+        <v>529</v>
+      </c>
+      <c r="J285">
+        <v>468.95</v>
+      </c>
+      <c r="K285">
+        <v>381.5</v>
+      </c>
+      <c r="L285">
+        <v>322.15</v>
+      </c>
+      <c r="M285">
+        <v>301.5</v>
+      </c>
+      <c r="N285">
+        <v>300</v>
+      </c>
+      <c r="O285">
+        <v>300</v>
+      </c>
+      <c r="P285">
+        <v>288.95</v>
+      </c>
+      <c r="Q285">
+        <v>358.6</v>
+      </c>
+      <c r="R285">
+        <v>459.85</v>
+      </c>
+      <c r="S285">
+        <v>527.13</v>
+      </c>
+      <c r="T285">
+        <v>560</v>
+      </c>
+      <c r="U285">
+        <v>548.5</v>
+      </c>
+      <c r="V285">
+        <v>535</v>
+      </c>
+      <c r="W285">
+        <v>528.2</v>
+      </c>
+      <c r="X285">
+        <v>525</v>
+      </c>
+      <c r="Y285">
+        <v>525</v>
+      </c>
+      <c r="Z285">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="286" spans="1:26">
+      <c r="A286" s="2">
+        <v>46306</v>
+      </c>
+      <c r="C286">
+        <v>469.5</v>
+      </c>
+      <c r="D286">
+        <v>469</v>
+      </c>
+      <c r="E286">
+        <v>468</v>
+      </c>
+      <c r="F286">
+        <v>465.81</v>
+      </c>
+      <c r="G286">
+        <v>468</v>
+      </c>
+      <c r="H286">
+        <v>474.87</v>
+      </c>
+      <c r="I286">
+        <v>480</v>
+      </c>
+      <c r="J286">
+        <v>450</v>
+      </c>
+      <c r="K286">
+        <v>435.1</v>
+      </c>
+      <c r="L286">
+        <v>428.4</v>
+      </c>
+      <c r="M286">
+        <v>436.05</v>
+      </c>
+      <c r="N286">
+        <v>440.53</v>
+      </c>
+      <c r="O286">
+        <v>439.9</v>
+      </c>
+      <c r="P286">
+        <v>442.25</v>
+      </c>
+      <c r="Q286">
+        <v>466.5</v>
+      </c>
+      <c r="R286">
+        <v>486.66</v>
+      </c>
+      <c r="S286">
+        <v>508</v>
+      </c>
+      <c r="T286">
+        <v>518.3200000000001</v>
+      </c>
+      <c r="U286">
+        <v>500</v>
+      </c>
+      <c r="V286">
+        <v>495</v>
+      </c>
+      <c r="W286">
+        <v>494.5</v>
+      </c>
+      <c r="X286">
+        <v>485</v>
+      </c>
+      <c r="Y286">
+        <v>485</v>
+      </c>
+      <c r="Z286">
+        <v>478.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel/2026/日前现货_发电侧小时电价.xlsx
+++ b/excel/2026/日前现货_发电侧小时电价.xlsx
@@ -1194,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z286"/>
+  <dimension ref="A1:Z291"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
@@ -23963,6 +23963,391 @@
         <v>478.5</v>
       </c>
     </row>
+    <row r="287" spans="1:26">
+      <c r="A287" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C287">
+        <v>499</v>
+      </c>
+      <c r="D287">
+        <v>500</v>
+      </c>
+      <c r="E287">
+        <v>480</v>
+      </c>
+      <c r="F287">
+        <v>479</v>
+      </c>
+      <c r="G287">
+        <v>488.56</v>
+      </c>
+      <c r="H287">
+        <v>498.92</v>
+      </c>
+      <c r="I287">
+        <v>500.37</v>
+      </c>
+      <c r="J287">
+        <v>450</v>
+      </c>
+      <c r="K287">
+        <v>396.65</v>
+      </c>
+      <c r="L287">
+        <v>350</v>
+      </c>
+      <c r="M287">
+        <v>336.86</v>
+      </c>
+      <c r="N287">
+        <v>333.15</v>
+      </c>
+      <c r="O287">
+        <v>317.57</v>
+      </c>
+      <c r="P287">
+        <v>350</v>
+      </c>
+      <c r="Q287">
+        <v>382</v>
+      </c>
+      <c r="R287">
+        <v>401.3</v>
+      </c>
+      <c r="S287">
+        <v>436.43</v>
+      </c>
+      <c r="T287">
+        <v>439</v>
+      </c>
+      <c r="U287">
+        <v>439.5</v>
+      </c>
+      <c r="V287">
+        <v>411.4</v>
+      </c>
+      <c r="W287">
+        <v>401.5</v>
+      </c>
+      <c r="X287">
+        <v>389</v>
+      </c>
+      <c r="Y287">
+        <v>380.5</v>
+      </c>
+      <c r="Z287">
+        <v>385.95</v>
+      </c>
+    </row>
+    <row r="288" spans="1:26">
+      <c r="A288" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C288">
+        <v>380</v>
+      </c>
+      <c r="D288">
+        <v>320.56</v>
+      </c>
+      <c r="E288">
+        <v>311</v>
+      </c>
+      <c r="F288">
+        <v>307</v>
+      </c>
+      <c r="G288">
+        <v>300</v>
+      </c>
+      <c r="H288">
+        <v>293.05</v>
+      </c>
+      <c r="I288">
+        <v>320</v>
+      </c>
+      <c r="J288">
+        <v>319.5</v>
+      </c>
+      <c r="K288">
+        <v>350.4</v>
+      </c>
+      <c r="L288">
+        <v>359.5</v>
+      </c>
+      <c r="M288">
+        <v>380</v>
+      </c>
+      <c r="N288">
+        <v>408.17</v>
+      </c>
+      <c r="O288">
+        <v>399.23</v>
+      </c>
+      <c r="P288">
+        <v>425.5</v>
+      </c>
+      <c r="Q288">
+        <v>403.53</v>
+      </c>
+      <c r="R288">
+        <v>379</v>
+      </c>
+      <c r="S288">
+        <v>368.55</v>
+      </c>
+      <c r="T288">
+        <v>350</v>
+      </c>
+      <c r="U288">
+        <v>344.24</v>
+      </c>
+      <c r="V288">
+        <v>332.5</v>
+      </c>
+      <c r="W288">
+        <v>330.5</v>
+      </c>
+      <c r="X288">
+        <v>328.09</v>
+      </c>
+      <c r="Y288">
+        <v>309.5</v>
+      </c>
+      <c r="Z288">
+        <v>220.5</v>
+      </c>
+    </row>
+    <row r="289" spans="1:26">
+      <c r="A289" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C289">
+        <v>329.91</v>
+      </c>
+      <c r="D289">
+        <v>262</v>
+      </c>
+      <c r="E289">
+        <v>193.38</v>
+      </c>
+      <c r="F289">
+        <v>194.5</v>
+      </c>
+      <c r="G289">
+        <v>182.5</v>
+      </c>
+      <c r="H289">
+        <v>264.85</v>
+      </c>
+      <c r="I289">
+        <v>300</v>
+      </c>
+      <c r="J289">
+        <v>259.8</v>
+      </c>
+      <c r="K289">
+        <v>199.5</v>
+      </c>
+      <c r="L289">
+        <v>199.5</v>
+      </c>
+      <c r="M289">
+        <v>100</v>
+      </c>
+      <c r="N289">
+        <v>199.5</v>
+      </c>
+      <c r="O289">
+        <v>197</v>
+      </c>
+      <c r="P289">
+        <v>200</v>
+      </c>
+      <c r="Q289">
+        <v>300</v>
+      </c>
+      <c r="R289">
+        <v>414</v>
+      </c>
+      <c r="S289">
+        <v>501.5</v>
+      </c>
+      <c r="T289">
+        <v>535.54</v>
+      </c>
+      <c r="U289">
+        <v>530</v>
+      </c>
+      <c r="V289">
+        <v>533.21</v>
+      </c>
+      <c r="W289">
+        <v>530</v>
+      </c>
+      <c r="X289">
+        <v>530</v>
+      </c>
+      <c r="Y289">
+        <v>530</v>
+      </c>
+      <c r="Z289">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="290" spans="1:26">
+      <c r="A290" s="2">
+        <v>46313</v>
+      </c>
+      <c r="C290">
+        <v>477.5</v>
+      </c>
+      <c r="D290">
+        <v>468.5</v>
+      </c>
+      <c r="E290">
+        <v>459</v>
+      </c>
+      <c r="F290">
+        <v>455</v>
+      </c>
+      <c r="G290">
+        <v>462.5</v>
+      </c>
+      <c r="H290">
+        <v>461.5</v>
+      </c>
+      <c r="I290">
+        <v>457</v>
+      </c>
+      <c r="J290">
+        <v>455.5</v>
+      </c>
+      <c r="K290">
+        <v>449.23</v>
+      </c>
+      <c r="L290">
+        <v>447.81</v>
+      </c>
+      <c r="M290">
+        <v>416.7</v>
+      </c>
+      <c r="N290">
+        <v>430.5</v>
+      </c>
+      <c r="O290">
+        <v>463.5</v>
+      </c>
+      <c r="P290">
+        <v>492.98</v>
+      </c>
+      <c r="Q290">
+        <v>502.6</v>
+      </c>
+      <c r="R290">
+        <v>497</v>
+      </c>
+      <c r="S290">
+        <v>488.34</v>
+      </c>
+      <c r="T290">
+        <v>493.1</v>
+      </c>
+      <c r="U290">
+        <v>484</v>
+      </c>
+      <c r="V290">
+        <v>475</v>
+      </c>
+      <c r="W290">
+        <v>474.5</v>
+      </c>
+      <c r="X290">
+        <v>470</v>
+      </c>
+      <c r="Y290">
+        <v>474</v>
+      </c>
+      <c r="Z290">
+        <v>463.5</v>
+      </c>
+    </row>
+    <row r="291" spans="1:26">
+      <c r="A291" s="2">
+        <v>46314</v>
+      </c>
+      <c r="C291">
+        <v>469</v>
+      </c>
+      <c r="D291">
+        <v>460</v>
+      </c>
+      <c r="E291">
+        <v>454</v>
+      </c>
+      <c r="F291">
+        <v>452.5</v>
+      </c>
+      <c r="G291">
+        <v>460</v>
+      </c>
+      <c r="H291">
+        <v>465</v>
+      </c>
+      <c r="I291">
+        <v>469.5</v>
+      </c>
+      <c r="J291">
+        <v>472.7</v>
+      </c>
+      <c r="K291">
+        <v>520</v>
+      </c>
+      <c r="L291">
+        <v>548.0700000000001</v>
+      </c>
+      <c r="M291">
+        <v>548.5</v>
+      </c>
+      <c r="N291">
+        <v>545.45</v>
+      </c>
+      <c r="O291">
+        <v>502.21</v>
+      </c>
+      <c r="P291">
+        <v>497.5</v>
+      </c>
+      <c r="Q291">
+        <v>479.8</v>
+      </c>
+      <c r="R291">
+        <v>469.5</v>
+      </c>
+      <c r="S291">
+        <v>470</v>
+      </c>
+      <c r="T291">
+        <v>469.2</v>
+      </c>
+      <c r="U291">
+        <v>447.25</v>
+      </c>
+      <c r="V291">
+        <v>430</v>
+      </c>
+      <c r="W291">
+        <v>421.5</v>
+      </c>
+      <c r="X291">
+        <v>360</v>
+      </c>
+      <c r="Y291">
+        <v>299.5</v>
+      </c>
+      <c r="Z291">
+        <v>261.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel/2026/日前现货_发电侧小时电价.xlsx
+++ b/excel/2026/日前现货_发电侧小时电价.xlsx
@@ -1194,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z291"/>
+  <dimension ref="A1:Z297"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
@@ -24348,6 +24348,468 @@
         <v>261.35</v>
       </c>
     </row>
+    <row r="292" spans="1:26">
+      <c r="A292" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C292">
+        <v>220</v>
+      </c>
+      <c r="D292">
+        <v>112</v>
+      </c>
+      <c r="E292">
+        <v>90.5</v>
+      </c>
+      <c r="F292">
+        <v>99.5</v>
+      </c>
+      <c r="G292">
+        <v>133.08</v>
+      </c>
+      <c r="H292">
+        <v>251.9</v>
+      </c>
+      <c r="I292">
+        <v>330.5</v>
+      </c>
+      <c r="J292">
+        <v>99.5</v>
+      </c>
+      <c r="K292">
+        <v>-29.67</v>
+      </c>
+      <c r="L292">
+        <v>-39.5</v>
+      </c>
+      <c r="M292">
+        <v>-45.5</v>
+      </c>
+      <c r="N292">
+        <v>-31</v>
+      </c>
+      <c r="O292">
+        <v>-29.5</v>
+      </c>
+      <c r="P292">
+        <v>-39.5</v>
+      </c>
+      <c r="Q292">
+        <v>-0.97</v>
+      </c>
+      <c r="R292">
+        <v>250.15</v>
+      </c>
+      <c r="S292">
+        <v>524.29</v>
+      </c>
+      <c r="T292">
+        <v>542.42</v>
+      </c>
+      <c r="U292">
+        <v>550</v>
+      </c>
+      <c r="V292">
+        <v>550</v>
+      </c>
+      <c r="W292">
+        <v>535.1</v>
+      </c>
+      <c r="X292">
+        <v>530</v>
+      </c>
+      <c r="Y292">
+        <v>531</v>
+      </c>
+      <c r="Z292">
+        <v>530.45</v>
+      </c>
+    </row>
+    <row r="293" spans="1:26">
+      <c r="A293" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C293">
+        <v>487.24</v>
+      </c>
+      <c r="D293">
+        <v>482</v>
+      </c>
+      <c r="E293">
+        <v>482</v>
+      </c>
+      <c r="F293">
+        <v>470</v>
+      </c>
+      <c r="G293">
+        <v>470</v>
+      </c>
+      <c r="H293">
+        <v>477</v>
+      </c>
+      <c r="I293">
+        <v>480</v>
+      </c>
+      <c r="J293">
+        <v>395.7</v>
+      </c>
+      <c r="K293">
+        <v>240.13</v>
+      </c>
+      <c r="L293">
+        <v>218.56</v>
+      </c>
+      <c r="M293">
+        <v>247.9</v>
+      </c>
+      <c r="N293">
+        <v>275.71</v>
+      </c>
+      <c r="O293">
+        <v>271.45</v>
+      </c>
+      <c r="P293">
+        <v>325.5</v>
+      </c>
+      <c r="Q293">
+        <v>436</v>
+      </c>
+      <c r="R293">
+        <v>479.4</v>
+      </c>
+      <c r="S293">
+        <v>507.16</v>
+      </c>
+      <c r="T293">
+        <v>504.27</v>
+      </c>
+      <c r="U293">
+        <v>499.5</v>
+      </c>
+      <c r="V293">
+        <v>492.1</v>
+      </c>
+      <c r="W293">
+        <v>489.6</v>
+      </c>
+      <c r="X293">
+        <v>488</v>
+      </c>
+      <c r="Y293">
+        <v>496.5</v>
+      </c>
+      <c r="Z293">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="294" spans="1:26">
+      <c r="A294" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C294">
+        <v>485</v>
+      </c>
+      <c r="D294">
+        <v>480</v>
+      </c>
+      <c r="E294">
+        <v>470</v>
+      </c>
+      <c r="F294">
+        <v>470</v>
+      </c>
+      <c r="G294">
+        <v>470</v>
+      </c>
+      <c r="H294">
+        <v>479.5</v>
+      </c>
+      <c r="I294">
+        <v>480</v>
+      </c>
+      <c r="J294">
+        <v>470</v>
+      </c>
+      <c r="K294">
+        <v>420.5</v>
+      </c>
+      <c r="L294">
+        <v>369</v>
+      </c>
+      <c r="M294">
+        <v>330</v>
+      </c>
+      <c r="N294">
+        <v>305.68</v>
+      </c>
+      <c r="O294">
+        <v>248.5</v>
+      </c>
+      <c r="P294">
+        <v>313.31</v>
+      </c>
+      <c r="Q294">
+        <v>360.7</v>
+      </c>
+      <c r="R294">
+        <v>449.15</v>
+      </c>
+      <c r="S294">
+        <v>506.2</v>
+      </c>
+      <c r="T294">
+        <v>507.49</v>
+      </c>
+      <c r="U294">
+        <v>499.15</v>
+      </c>
+      <c r="V294">
+        <v>510</v>
+      </c>
+      <c r="W294">
+        <v>500</v>
+      </c>
+      <c r="X294">
+        <v>502.5</v>
+      </c>
+      <c r="Y294">
+        <v>508</v>
+      </c>
+      <c r="Z294">
+        <v>494.29</v>
+      </c>
+    </row>
+    <row r="295" spans="1:26">
+      <c r="A295" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C295">
+        <v>485</v>
+      </c>
+      <c r="D295">
+        <v>465</v>
+      </c>
+      <c r="E295">
+        <v>469.5</v>
+      </c>
+      <c r="F295">
+        <v>465</v>
+      </c>
+      <c r="G295">
+        <v>469</v>
+      </c>
+      <c r="H295">
+        <v>470</v>
+      </c>
+      <c r="I295">
+        <v>465</v>
+      </c>
+      <c r="J295">
+        <v>422.38</v>
+      </c>
+      <c r="K295">
+        <v>331.65</v>
+      </c>
+      <c r="L295">
+        <v>192.95</v>
+      </c>
+      <c r="M295">
+        <v>152</v>
+      </c>
+      <c r="N295">
+        <v>154.39</v>
+      </c>
+      <c r="O295">
+        <v>170.5</v>
+      </c>
+      <c r="P295">
+        <v>300</v>
+      </c>
+      <c r="Q295">
+        <v>372.65</v>
+      </c>
+      <c r="R295">
+        <v>464.02</v>
+      </c>
+      <c r="S295">
+        <v>503.5</v>
+      </c>
+      <c r="T295">
+        <v>491</v>
+      </c>
+      <c r="U295">
+        <v>490.18</v>
+      </c>
+      <c r="V295">
+        <v>483.4</v>
+      </c>
+      <c r="W295">
+        <v>486.3</v>
+      </c>
+      <c r="X295">
+        <v>488.77</v>
+      </c>
+      <c r="Y295">
+        <v>492.5</v>
+      </c>
+      <c r="Z295">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="296" spans="1:26">
+      <c r="A296" s="2">
+        <v>46319</v>
+      </c>
+      <c r="C296">
+        <v>465.5</v>
+      </c>
+      <c r="D296">
+        <v>456</v>
+      </c>
+      <c r="E296">
+        <v>445.85</v>
+      </c>
+      <c r="F296">
+        <v>438.45</v>
+      </c>
+      <c r="G296">
+        <v>440.5</v>
+      </c>
+      <c r="H296">
+        <v>441.55</v>
+      </c>
+      <c r="I296">
+        <v>420.95</v>
+      </c>
+      <c r="J296">
+        <v>397</v>
+      </c>
+      <c r="K296">
+        <v>287.94</v>
+      </c>
+      <c r="L296">
+        <v>181.29</v>
+      </c>
+      <c r="M296">
+        <v>50.07</v>
+      </c>
+      <c r="N296">
+        <v>100</v>
+      </c>
+      <c r="O296">
+        <v>102.73</v>
+      </c>
+      <c r="P296">
+        <v>127</v>
+      </c>
+      <c r="Q296">
+        <v>249.1</v>
+      </c>
+      <c r="R296">
+        <v>391.43</v>
+      </c>
+      <c r="S296">
+        <v>469</v>
+      </c>
+      <c r="T296">
+        <v>476.31</v>
+      </c>
+      <c r="U296">
+        <v>469.5</v>
+      </c>
+      <c r="V296">
+        <v>469.05</v>
+      </c>
+      <c r="W296">
+        <v>469.5</v>
+      </c>
+      <c r="X296">
+        <v>469.5</v>
+      </c>
+      <c r="Y296">
+        <v>469.4</v>
+      </c>
+      <c r="Z296">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="297" spans="1:26">
+      <c r="A297" s="2">
+        <v>46320</v>
+      </c>
+      <c r="C297">
+        <v>460.9</v>
+      </c>
+      <c r="D297">
+        <v>453</v>
+      </c>
+      <c r="E297">
+        <v>442.85</v>
+      </c>
+      <c r="F297">
+        <v>438.05</v>
+      </c>
+      <c r="G297">
+        <v>453</v>
+      </c>
+      <c r="H297">
+        <v>459.5</v>
+      </c>
+      <c r="I297">
+        <v>460</v>
+      </c>
+      <c r="J297">
+        <v>460</v>
+      </c>
+      <c r="K297">
+        <v>459</v>
+      </c>
+      <c r="L297">
+        <v>458.29</v>
+      </c>
+      <c r="M297">
+        <v>449.14</v>
+      </c>
+      <c r="N297">
+        <v>396.85</v>
+      </c>
+      <c r="O297">
+        <v>394.9</v>
+      </c>
+      <c r="P297">
+        <v>460</v>
+      </c>
+      <c r="Q297">
+        <v>460</v>
+      </c>
+      <c r="R297">
+        <v>459</v>
+      </c>
+      <c r="S297">
+        <v>464.4</v>
+      </c>
+      <c r="T297">
+        <v>460</v>
+      </c>
+      <c r="U297">
+        <v>459</v>
+      </c>
+      <c r="V297">
+        <v>459.5</v>
+      </c>
+      <c r="W297">
+        <v>455</v>
+      </c>
+      <c r="X297">
+        <v>455</v>
+      </c>
+      <c r="Y297">
+        <v>440.55</v>
+      </c>
+      <c r="Z297">
+        <v>423.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
